--- a/策划/数值文档/unit_cs-pack.xlsx
+++ b/策划/数值文档/unit_cs-pack.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
   <si>
     <t>id</t>
   </si>
@@ -125,6 +125,15 @@
   </si>
   <si>
     <t>flying</t>
+  </si>
+  <si>
+    <t>spawn_stagger_ms</t>
+  </si>
+  <si>
+    <t>jump_height_mt</t>
+  </si>
+  <si>
+    <t>jump_speed</t>
   </si>
   <si>
     <t>int</t>
@@ -1238,344 +1247,371 @@
       <c r="AK1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="P2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Q2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="S2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="U2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="V2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="W2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="X2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Y2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="Z2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AA2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AB2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AC2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AD2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AE2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AF2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AH2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AI2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AK2" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="P3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="S3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="T3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="U3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="W3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="X3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Y3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Z3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AA3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AC3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AE3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AF3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AG3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AH3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AI3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AK3" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="P4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="R4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="S4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="T4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="U4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="V4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="W4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="X4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="Y4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Z4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AA4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="AB4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AC4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AD4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AE4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AF4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="AG4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AH4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AI4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AJ4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AK4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -1583,10 +1619,10 @@
         <v>26020001</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1637,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1655,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="Z5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA5">
         <v>0</v>
@@ -1670,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AF5">
         <v>1</v>
@@ -1685,9 +1721,18 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
         <v>0</v>
       </c>
     </row>
@@ -1696,10 +1741,10 @@
         <v>26020002</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1750,10 +1795,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="U6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1768,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="Z6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA6">
         <v>0</v>
@@ -1783,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="AF6">
         <v>2</v>
@@ -1798,9 +1843,18 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
         <v>0</v>
       </c>
     </row>
@@ -1809,10 +1863,10 @@
         <v>26020003</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1863,10 +1917,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="U7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -1881,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA7">
         <v>0</v>
@@ -1896,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1911,9 +1965,18 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
         <v>0</v>
       </c>
     </row>
@@ -1922,10 +1985,10 @@
         <v>26020004</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1976,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -1994,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="Z8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA8">
         <v>0</v>
@@ -2009,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="AF8">
         <v>4</v>
@@ -2024,9 +2087,18 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
         <v>0</v>
       </c>
     </row>
@@ -2035,10 +2107,10 @@
         <v>26020005</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2089,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2107,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="Z9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA9">
         <v>0</v>
@@ -2122,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2137,9 +2209,18 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
         <v>0</v>
       </c>
     </row>
@@ -2148,10 +2229,10 @@
         <v>26020006</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2202,10 +2283,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2220,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="Z10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA10">
         <v>0</v>
@@ -2235,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AF10">
         <v>3</v>
@@ -2250,9 +2331,18 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
         <v>0</v>
       </c>
     </row>
@@ -2261,10 +2351,10 @@
         <v>26020007</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -2315,10 +2405,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="U11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -2333,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="Z11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA11">
         <v>0</v>
@@ -2348,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -2363,9 +2453,18 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
         <v>0</v>
       </c>
     </row>
@@ -2374,10 +2473,10 @@
         <v>26020008</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2428,10 +2527,10 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -2446,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="Z12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA12">
         <v>0</v>
@@ -2461,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF12">
         <v>1</v>
@@ -2476,9 +2575,18 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
         <v>0</v>
       </c>
     </row>
@@ -2487,10 +2595,10 @@
         <v>26020009</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -2541,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -2559,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="Z13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA13">
         <v>0</v>
@@ -2574,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF13">
         <v>1</v>
@@ -2589,9 +2697,18 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
         <v>0</v>
       </c>
     </row>
@@ -2600,10 +2717,10 @@
         <v>26020010</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -2654,10 +2771,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="U14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -2672,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="Z14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA14">
         <v>0</v>
@@ -2687,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AF14">
         <v>3</v>
@@ -2702,10 +2819,19 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AK14">
         <v>1</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2713,10 +2839,10 @@
         <v>26020011</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -2767,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="U15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -2785,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA15">
         <v>0</v>
@@ -2800,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF15">
         <v>0</v>
@@ -2815,10 +2941,19 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AK15">
         <v>1</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2826,10 +2961,10 @@
         <v>26020012</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -2880,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="U16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -2898,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="Z16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA16">
         <v>0</v>
@@ -2913,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AF16">
         <v>6</v>
@@ -2928,10 +3063,19 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="AK16">
         <v>1</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2939,10 +3083,10 @@
         <v>26020013</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2993,10 +3137,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U17" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -3011,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="Z17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA17">
         <v>0</v>
@@ -3026,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AF17">
         <v>1</v>
@@ -3041,10 +3185,19 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="AK17">
         <v>1</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3052,10 +3205,10 @@
         <v>26020014</v>
       </c>
       <c r="B18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -3106,10 +3259,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="U18" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -3124,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Z18" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AA18">
         <v>4</v>
@@ -3139,7 +3292,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AF18">
         <v>1</v>
@@ -3154,9 +3307,18 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
         <v>0</v>
       </c>
     </row>
@@ -3165,10 +3327,10 @@
         <v>26020015</v>
       </c>
       <c r="B19" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -3219,10 +3381,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -3237,7 +3399,7 @@
         <v>0</v>
       </c>
       <c r="Z19" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA19">
         <v>0</v>
@@ -3252,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AF19">
         <v>5</v>
@@ -3267,9 +3429,18 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
         <v>0</v>
       </c>
     </row>
@@ -3278,10 +3449,10 @@
         <v>26020016</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -3332,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -3350,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="Z20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA20">
         <v>0</v>
@@ -3365,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF20">
         <v>0</v>
@@ -3380,9 +3551,18 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
         <v>0</v>
       </c>
     </row>
@@ -3391,10 +3571,10 @@
         <v>26020017</v>
       </c>
       <c r="B21" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -3445,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -3463,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="Z21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA21">
         <v>0</v>
@@ -3478,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AF21">
         <v>3</v>
@@ -3493,9 +3673,18 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
         <v>0</v>
       </c>
     </row>
@@ -3504,10 +3693,10 @@
         <v>26020018</v>
       </c>
       <c r="B22" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3558,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -3576,7 +3765,7 @@
         <v>0</v>
       </c>
       <c r="Z22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA22">
         <v>0</v>
@@ -3591,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -3606,9 +3795,18 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
         <v>0</v>
       </c>
     </row>
@@ -3617,10 +3815,10 @@
         <v>26020019</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -3671,10 +3869,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -3689,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA23">
         <v>0</v>
@@ -3704,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AF23">
         <v>15</v>
@@ -3719,9 +3917,18 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
         <v>0</v>
       </c>
     </row>
@@ -3730,10 +3937,10 @@
         <v>26020020</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3784,10 +3991,10 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -3802,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -3817,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AF24">
         <v>1</v>
@@ -3832,9 +4039,18 @@
         <v>2000</v>
       </c>
       <c r="AJ24" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
         <v>0</v>
       </c>
     </row>
@@ -3843,10 +4059,10 @@
         <v>26020021</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3897,10 +4113,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="U25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -3915,7 +4131,7 @@
         <v>0</v>
       </c>
       <c r="Z25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA25">
         <v>0</v>
@@ -3930,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AF25">
         <v>1</v>
@@ -3945,9 +4161,18 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
         <v>0</v>
       </c>
     </row>
@@ -3956,10 +4181,10 @@
         <v>26020022</v>
       </c>
       <c r="B26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C26" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4010,10 +4235,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="U26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -4028,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA26">
         <v>0</v>
@@ -4043,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AF26">
         <v>1</v>
@@ -4058,9 +4283,18 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
         <v>0</v>
       </c>
     </row>
@@ -4069,10 +4303,10 @@
         <v>26020023</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4123,10 +4357,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="U27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -4141,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="Z27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA27">
         <v>0</v>
@@ -4156,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="AF27">
         <v>1</v>
@@ -4171,10 +4405,19 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK27">
         <v>1</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4182,10 +4425,10 @@
         <v>26020024</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C28" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -4236,10 +4479,10 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -4254,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="Z28" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -4269,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AF28">
         <v>1</v>
@@ -4284,10 +4527,19 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AK28">
         <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>4000</v>
+      </c>
+      <c r="AN28">
+        <v>160</v>
       </c>
     </row>
     <row r="29">
@@ -4295,10 +4547,10 @@
         <v>26020025</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -4349,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="U29" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -4367,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="Z29" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA29">
         <v>0</v>
@@ -4382,7 +4634,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AF29">
         <v>1</v>
@@ -4397,9 +4649,18 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+      <c r="AN29">
         <v>0</v>
       </c>
     </row>
@@ -4408,10 +4669,10 @@
         <v>26020026</v>
       </c>
       <c r="B30" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C30" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -4462,10 +4723,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -4480,7 +4741,7 @@
         <v>0</v>
       </c>
       <c r="Z30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -4495,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AF30">
         <v>1</v>
@@ -4510,9 +4771,18 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+      <c r="AN30">
         <v>0</v>
       </c>
     </row>
@@ -4521,10 +4791,10 @@
         <v>26020027</v>
       </c>
       <c r="B31" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -4575,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U31" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="V31">
         <v>1</v>
@@ -4593,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="Z31" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA31">
         <v>0</v>
@@ -4608,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AF31">
         <v>1</v>
@@ -4623,9 +4893,18 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+      <c r="AN31">
         <v>0</v>
       </c>
     </row>
@@ -4634,10 +4913,10 @@
         <v>26020028</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -4688,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -4706,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="Z32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA32">
         <v>0</v>
@@ -4721,7 +5000,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AF32">
         <v>1</v>
@@ -4736,10 +5015,19 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AK32">
         <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>4000</v>
+      </c>
+      <c r="AN32">
+        <v>160</v>
       </c>
     </row>
     <row r="33">
@@ -4747,10 +5035,10 @@
         <v>26020029</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C33" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -4801,10 +5089,10 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="U33" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -4819,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="Z33" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA33">
         <v>0</v>
@@ -4834,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AF33">
         <v>1</v>
@@ -4849,9 +5137,18 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+      <c r="AN33">
         <v>0</v>
       </c>
     </row>
@@ -4860,10 +5157,10 @@
         <v>26020030</v>
       </c>
       <c r="B34" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -4914,10 +5211,10 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="U34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -4932,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="Z34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA34">
         <v>0</v>
@@ -4947,7 +5244,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AF34">
         <v>1</v>
@@ -4962,9 +5259,18 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
         <v>0</v>
       </c>
     </row>
@@ -4973,10 +5279,10 @@
         <v>26020031</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -5027,10 +5333,10 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="U35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -5045,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="Z35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA35">
         <v>0</v>
@@ -5060,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AF35">
         <v>1</v>
@@ -5075,9 +5381,18 @@
         <v>2500</v>
       </c>
       <c r="AJ35" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+      <c r="AN35">
         <v>0</v>
       </c>
     </row>
@@ -5086,10 +5401,10 @@
         <v>26020032</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C36" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -5140,10 +5455,10 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -5158,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="Z36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA36">
         <v>0</v>
@@ -5173,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AF36">
         <v>1</v>
@@ -5188,10 +5503,19 @@
         <v>1100</v>
       </c>
       <c r="AJ36" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AK36">
         <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>4000</v>
+      </c>
+      <c r="AN36">
+        <v>160</v>
       </c>
     </row>
     <row r="37">
@@ -5199,10 +5523,10 @@
         <v>26020033</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C37" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -5253,10 +5577,10 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="U37" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="V37">
         <v>6</v>
@@ -5271,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="Z37" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA37">
         <v>0</v>
@@ -5286,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AF37">
         <v>1</v>
@@ -5301,10 +5625,19 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AK37">
         <v>1</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -5312,10 +5645,10 @@
         <v>26020034</v>
       </c>
       <c r="B38" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C38" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -5366,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="U38" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -5384,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="Z38" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA38">
         <v>0</v>
@@ -5399,7 +5732,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AF38">
         <v>1</v>
@@ -5414,9 +5747,18 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
         <v>0</v>
       </c>
     </row>
@@ -5425,10 +5767,10 @@
         <v>26020035</v>
       </c>
       <c r="B39" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C39" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -5479,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="U39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -5497,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="Z39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA39">
         <v>0</v>
@@ -5512,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AF39">
         <v>1</v>
@@ -5527,9 +5869,18 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
         <v>0</v>
       </c>
     </row>
@@ -5538,10 +5889,10 @@
         <v>26020036</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C40" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -5592,10 +5943,10 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -5610,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="Z40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA40">
         <v>0</v>
@@ -5625,7 +5976,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AF40">
         <v>1</v>
@@ -5640,9 +5991,18 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40">
         <v>0</v>
       </c>
     </row>
@@ -5651,10 +6011,10 @@
         <v>26020037</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C41" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -5705,10 +6065,10 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="U41" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -5723,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="Z41" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA41">
         <v>0</v>
@@ -5738,7 +6098,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="AF41">
         <v>1</v>
@@ -5753,9 +6113,18 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
         <v>0</v>
       </c>
     </row>
@@ -5764,10 +6133,10 @@
         <v>26020038</v>
       </c>
       <c r="B42" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -5818,10 +6187,10 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U42" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="V42">
         <v>2</v>
@@ -5836,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="Z42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA42">
         <v>0</v>
@@ -5851,7 +6220,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AF42">
         <v>1</v>
@@ -5866,10 +6235,19 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AK42">
         <v>0</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>4000</v>
+      </c>
+      <c r="AN42">
+        <v>160</v>
       </c>
     </row>
     <row r="43">
@@ -5877,10 +6255,10 @@
         <v>26020039</v>
       </c>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C43" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -5931,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="U43" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -5949,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="Z43" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA43">
         <v>0</v>
@@ -5964,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AF43">
         <v>1</v>
@@ -5979,10 +6357,19 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AK43">
         <v>1</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
+      <c r="AN43">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5990,10 +6377,10 @@
         <v>26020040</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C44" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -6044,10 +6431,10 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="U44" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V44">
         <v>0</v>
@@ -6062,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="Z44" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -6077,7 +6464,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AF44">
         <v>1</v>
@@ -6092,9 +6479,18 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AK44">
+        <v>0</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>0</v>
+      </c>
+      <c r="AN44">
         <v>0</v>
       </c>
     </row>
@@ -6103,10 +6499,10 @@
         <v>26020041</v>
       </c>
       <c r="B45" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -6157,10 +6553,10 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -6175,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="Z45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA45">
         <v>0</v>
@@ -6190,7 +6586,7 @@
         <v>0</v>
       </c>
       <c r="AE45" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AF45">
         <v>1</v>
@@ -6205,9 +6601,18 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
+      </c>
+      <c r="AN45">
         <v>0</v>
       </c>
     </row>
@@ -6216,10 +6621,10 @@
         <v>26020042</v>
       </c>
       <c r="B46" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C46" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -6270,10 +6675,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="U46" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V46">
         <v>0</v>
@@ -6288,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="Z46" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA46">
         <v>0</v>
@@ -6303,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="AE46" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AF46">
         <v>1</v>
@@ -6318,9 +6723,18 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>0</v>
+      </c>
+      <c r="AN46">
         <v>0</v>
       </c>
     </row>
@@ -6329,10 +6743,10 @@
         <v>26020043</v>
       </c>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -6383,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U47" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -6401,7 +6815,7 @@
         <v>0</v>
       </c>
       <c r="Z47" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA47">
         <v>0</v>
@@ -6416,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="AE47" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AF47">
         <v>1</v>
@@ -6431,9 +6845,18 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>0</v>
+      </c>
+      <c r="AN47">
         <v>0</v>
       </c>
     </row>
@@ -6442,10 +6865,10 @@
         <v>26020044</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C48" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -6496,10 +6919,10 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U48" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -6514,7 +6937,7 @@
         <v>0</v>
       </c>
       <c r="Z48" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA48">
         <v>0</v>
@@ -6529,7 +6952,7 @@
         <v>0</v>
       </c>
       <c r="AE48" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AF48">
         <v>5</v>
@@ -6544,10 +6967,19 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AK48">
         <v>1</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>0</v>
+      </c>
+      <c r="AN48">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -6555,10 +6987,10 @@
         <v>26020045</v>
       </c>
       <c r="B49" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -6609,10 +7041,10 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U49" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V49">
         <v>0</v>
@@ -6627,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="Z49" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA49">
         <v>0</v>
@@ -6642,7 +7074,7 @@
         <v>0</v>
       </c>
       <c r="AE49" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF49">
         <v>0</v>
@@ -6657,10 +7089,19 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK49">
         <v>1</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>0</v>
+      </c>
+      <c r="AN49">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -6668,10 +7109,10 @@
         <v>26020046</v>
       </c>
       <c r="B50" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C50" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -6722,10 +7163,10 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U50" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V50">
         <v>0</v>
@@ -6740,7 +7181,7 @@
         <v>0</v>
       </c>
       <c r="Z50" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA50">
         <v>1</v>
@@ -6755,7 +7196,7 @@
         <v>1</v>
       </c>
       <c r="AE50" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AF50">
         <v>1</v>
@@ -6770,9 +7211,18 @@
         <v>1300</v>
       </c>
       <c r="AJ50" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="AK50">
+        <v>0</v>
+      </c>
+      <c r="AL50">
+        <v>0</v>
+      </c>
+      <c r="AM50">
+        <v>0</v>
+      </c>
+      <c r="AN50">
         <v>0</v>
       </c>
     </row>
@@ -6781,10 +7231,10 @@
         <v>26020047</v>
       </c>
       <c r="B51" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C51" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -6835,41 +7285,41 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="U51" t="s">
+        <v>226</v>
+      </c>
+      <c r="V51">
+        <v>1</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="s">
         <v>223</v>
       </c>
-      <c r="V51">
-        <v>1</v>
-      </c>
-      <c r="W51">
-        <v>0</v>
-      </c>
-      <c r="X51">
-        <v>0</v>
-      </c>
-      <c r="Y51">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA51">
-        <v>0</v>
-      </c>
-      <c r="AB51">
-        <v>0</v>
-      </c>
-      <c r="AC51">
-        <v>0</v>
-      </c>
-      <c r="AD51">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="s">
-        <v>220</v>
-      </c>
       <c r="AF51">
         <v>1</v>
       </c>
@@ -6883,9 +7333,18 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AK51">
+        <v>0</v>
+      </c>
+      <c r="AL51">
+        <v>0</v>
+      </c>
+      <c r="AM51">
+        <v>0</v>
+      </c>
+      <c r="AN51">
         <v>0</v>
       </c>
     </row>
@@ -6894,10 +7353,10 @@
         <v>26020048</v>
       </c>
       <c r="B52" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C52" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -6948,10 +7407,10 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="U52" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -6966,7 +7425,7 @@
         <v>30000</v>
       </c>
       <c r="Z52" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA52">
         <v>0</v>
@@ -6981,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="AE52" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF52">
         <v>0</v>
@@ -6996,9 +7455,18 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AK52">
+        <v>0</v>
+      </c>
+      <c r="AL52">
+        <v>0</v>
+      </c>
+      <c r="AM52">
+        <v>0</v>
+      </c>
+      <c r="AN52">
         <v>0</v>
       </c>
     </row>
@@ -7007,10 +7475,10 @@
         <v>26020049</v>
       </c>
       <c r="B53" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C53" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -7061,10 +7529,10 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U53" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="V53">
         <v>1</v>
@@ -7079,7 +7547,7 @@
         <v>29000</v>
       </c>
       <c r="Z53" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AA53">
         <v>3</v>
@@ -7088,30 +7556,39 @@
         <v>0</v>
       </c>
       <c r="AC53">
+        <v>10000</v>
+      </c>
+      <c r="AD53">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF53">
+        <v>0</v>
+      </c>
+      <c r="AG53">
+        <v>0</v>
+      </c>
+      <c r="AH53">
+        <v>0</v>
+      </c>
+      <c r="AI53">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>234</v>
+      </c>
+      <c r="AK53">
+        <v>0</v>
+      </c>
+      <c r="AL53">
         <v>500</v>
       </c>
-      <c r="AD53">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF53">
-        <v>0</v>
-      </c>
-      <c r="AG53">
-        <v>0</v>
-      </c>
-      <c r="AH53">
-        <v>0</v>
-      </c>
-      <c r="AI53">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="s">
-        <v>231</v>
-      </c>
-      <c r="AK53">
+      <c r="AM53">
+        <v>0</v>
+      </c>
+      <c r="AN53">
         <v>0</v>
       </c>
     </row>
@@ -7120,10 +7597,10 @@
         <v>26020050</v>
       </c>
       <c r="B54" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C54" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -7174,10 +7651,10 @@
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="U54" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V54">
         <v>0</v>
@@ -7192,7 +7669,7 @@
         <v>30000</v>
       </c>
       <c r="Z54" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA54">
         <v>0</v>
@@ -7207,7 +7684,7 @@
         <v>0</v>
       </c>
       <c r="AE54" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF54">
         <v>0</v>
@@ -7222,9 +7699,18 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AK54">
+        <v>0</v>
+      </c>
+      <c r="AL54">
+        <v>0</v>
+      </c>
+      <c r="AM54">
+        <v>0</v>
+      </c>
+      <c r="AN54">
         <v>0</v>
       </c>
     </row>
@@ -7233,10 +7719,10 @@
         <v>26020051</v>
       </c>
       <c r="B55" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C55" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -7287,10 +7773,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U55" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V55">
         <v>0</v>
@@ -7305,7 +7791,7 @@
         <v>30000</v>
       </c>
       <c r="Z55" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA55">
         <v>0</v>
@@ -7320,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="AE55" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF55">
         <v>0</v>
@@ -7335,9 +7821,18 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AK55">
+        <v>0</v>
+      </c>
+      <c r="AL55">
+        <v>0</v>
+      </c>
+      <c r="AM55">
+        <v>0</v>
+      </c>
+      <c r="AN55">
         <v>0</v>
       </c>
     </row>
@@ -7346,10 +7841,10 @@
         <v>26020052</v>
       </c>
       <c r="B56" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C56" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -7400,10 +7895,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="U56" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="V56">
         <v>1</v>
@@ -7418,7 +7913,7 @@
         <v>30000</v>
       </c>
       <c r="Z56" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA56">
         <v>0</v>
@@ -7433,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="AE56" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF56">
         <v>0</v>
@@ -7448,9 +7943,18 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AK56">
+        <v>0</v>
+      </c>
+      <c r="AL56">
+        <v>0</v>
+      </c>
+      <c r="AM56">
+        <v>0</v>
+      </c>
+      <c r="AN56">
         <v>0</v>
       </c>
     </row>
@@ -7459,10 +7963,10 @@
         <v>26020053</v>
       </c>
       <c r="B57" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C57" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -7513,10 +8017,10 @@
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U57" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="V57">
         <v>1</v>
@@ -7531,7 +8035,7 @@
         <v>30000</v>
       </c>
       <c r="Z57" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AA57">
         <v>3</v>
@@ -7540,30 +8044,39 @@
         <v>0</v>
       </c>
       <c r="AC57">
+        <v>14000</v>
+      </c>
+      <c r="AD57">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF57">
+        <v>0</v>
+      </c>
+      <c r="AG57">
+        <v>0</v>
+      </c>
+      <c r="AH57">
+        <v>0</v>
+      </c>
+      <c r="AI57">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="s">
+        <v>249</v>
+      </c>
+      <c r="AK57">
+        <v>0</v>
+      </c>
+      <c r="AL57">
         <v>500</v>
       </c>
-      <c r="AD57">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF57">
-        <v>0</v>
-      </c>
-      <c r="AG57">
-        <v>0</v>
-      </c>
-      <c r="AH57">
-        <v>0</v>
-      </c>
-      <c r="AI57">
-        <v>0</v>
-      </c>
-      <c r="AJ57" t="s">
-        <v>246</v>
-      </c>
-      <c r="AK57">
+      <c r="AM57">
+        <v>0</v>
+      </c>
+      <c r="AN57">
         <v>0</v>
       </c>
     </row>
@@ -7572,10 +8085,10 @@
         <v>26020054</v>
       </c>
       <c r="B58" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C58" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -7626,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U58" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V58">
         <v>0</v>
@@ -7644,7 +8157,7 @@
         <v>30000</v>
       </c>
       <c r="Z58" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA58">
         <v>0</v>
@@ -7659,7 +8172,7 @@
         <v>0</v>
       </c>
       <c r="AE58" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF58">
         <v>0</v>
@@ -7674,9 +8187,18 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AK58">
+        <v>0</v>
+      </c>
+      <c r="AL58">
+        <v>0</v>
+      </c>
+      <c r="AM58">
+        <v>0</v>
+      </c>
+      <c r="AN58">
         <v>0</v>
       </c>
     </row>
@@ -7685,10 +8207,10 @@
         <v>26020055</v>
       </c>
       <c r="B59" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C59" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -7739,10 +8261,10 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U59" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V59">
         <v>0</v>
@@ -7757,7 +8279,7 @@
         <v>65000</v>
       </c>
       <c r="Z59" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA59">
         <v>0</v>
@@ -7772,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="AE59" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF59">
         <v>0</v>
@@ -7787,9 +8309,18 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AK59">
+        <v>0</v>
+      </c>
+      <c r="AL59">
+        <v>0</v>
+      </c>
+      <c r="AM59">
+        <v>0</v>
+      </c>
+      <c r="AN59">
         <v>0</v>
       </c>
     </row>
@@ -7798,10 +8329,10 @@
         <v>26020056</v>
       </c>
       <c r="B60" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C60" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -7852,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="U60" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -7870,7 +8401,7 @@
         <v>30000</v>
       </c>
       <c r="Z60" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA60">
         <v>0</v>
@@ -7885,7 +8416,7 @@
         <v>0</v>
       </c>
       <c r="AE60" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF60">
         <v>0</v>
@@ -7900,9 +8431,18 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AK60">
+        <v>0</v>
+      </c>
+      <c r="AL60">
+        <v>0</v>
+      </c>
+      <c r="AM60">
+        <v>0</v>
+      </c>
+      <c r="AN60">
         <v>0</v>
       </c>
     </row>
@@ -7911,10 +8451,10 @@
         <v>26020057</v>
       </c>
       <c r="B61" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C61" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -7965,10 +8505,10 @@
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U61" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="V61">
         <v>4</v>
@@ -7983,7 +8523,7 @@
         <v>30000</v>
       </c>
       <c r="Z61" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AA61">
         <v>2</v>
@@ -7992,30 +8532,39 @@
         <v>0</v>
       </c>
       <c r="AC61">
+        <v>3500</v>
+      </c>
+      <c r="AD61">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
+      <c r="AH61">
+        <v>0</v>
+      </c>
+      <c r="AI61">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
         <v>500</v>
       </c>
-      <c r="AD61">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF61">
-        <v>0</v>
-      </c>
-      <c r="AG61">
-        <v>0</v>
-      </c>
-      <c r="AH61">
-        <v>0</v>
-      </c>
-      <c r="AI61">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="s">
-        <v>259</v>
-      </c>
-      <c r="AK61">
+      <c r="AM61">
+        <v>0</v>
+      </c>
+      <c r="AN61">
         <v>0</v>
       </c>
     </row>
@@ -8024,10 +8573,10 @@
         <v>26020058</v>
       </c>
       <c r="B62" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C62" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -8078,10 +8627,10 @@
         <v>0</v>
       </c>
       <c r="T62" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="U62" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V62">
         <v>0</v>
@@ -8096,7 +8645,7 @@
         <v>0</v>
       </c>
       <c r="Z62" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA62">
         <v>0</v>
@@ -8111,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="AE62" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF62">
         <v>0</v>
@@ -8126,9 +8675,18 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62">
+        <v>0</v>
+      </c>
+      <c r="AM62">
+        <v>0</v>
+      </c>
+      <c r="AN62">
         <v>0</v>
       </c>
     </row>
@@ -8137,10 +8695,10 @@
         <v>26020059</v>
       </c>
       <c r="B63" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C63" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -8191,57 +8749,66 @@
         <v>0</v>
       </c>
       <c r="T63" t="s">
+        <v>269</v>
+      </c>
+      <c r="U63" t="s">
+        <v>82</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
+      <c r="AH63">
+        <v>0</v>
+      </c>
+      <c r="AI63">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="s">
         <v>266</v>
       </c>
-      <c r="U63" t="s">
-        <v>79</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA63">
-        <v>0</v>
-      </c>
-      <c r="AB63">
-        <v>0</v>
-      </c>
-      <c r="AC63">
-        <v>0</v>
-      </c>
-      <c r="AD63">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF63">
-        <v>0</v>
-      </c>
-      <c r="AG63">
-        <v>0</v>
-      </c>
-      <c r="AH63">
-        <v>0</v>
-      </c>
-      <c r="AI63">
-        <v>0</v>
-      </c>
-      <c r="AJ63" t="s">
-        <v>263</v>
-      </c>
       <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>0</v>
+      </c>
+      <c r="AN63">
         <v>0</v>
       </c>
     </row>
@@ -8250,10 +8817,10 @@
         <v>26020060</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -8304,10 +8871,10 @@
         <v>0</v>
       </c>
       <c r="T64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V64">
         <v>0</v>
@@ -8322,7 +8889,7 @@
         <v>0</v>
       </c>
       <c r="Z64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA64">
         <v>0</v>
@@ -8337,7 +8904,7 @@
         <v>0</v>
       </c>
       <c r="AE64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF64">
         <v>0</v>
@@ -8352,9 +8919,18 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>0</v>
+      </c>
+      <c r="AN64">
         <v>0</v>
       </c>
     </row>
@@ -8363,10 +8939,10 @@
         <v>26020061</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D65">
         <v>3</v>
@@ -8417,10 +8993,10 @@
         <v>0</v>
       </c>
       <c r="T65" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U65" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -8435,7 +9011,7 @@
         <v>0</v>
       </c>
       <c r="Z65" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA65">
         <v>0</v>
@@ -8450,7 +9026,7 @@
         <v>0</v>
       </c>
       <c r="AE65" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF65">
         <v>0</v>
@@ -8465,9 +9041,18 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>0</v>
+      </c>
+      <c r="AN65">
         <v>0</v>
       </c>
     </row>
@@ -8476,10 +9061,10 @@
         <v>26020062</v>
       </c>
       <c r="B66" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -8530,10 +9115,10 @@
         <v>0</v>
       </c>
       <c r="T66" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U66" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V66">
         <v>0</v>
@@ -8548,7 +9133,7 @@
         <v>0</v>
       </c>
       <c r="Z66" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA66">
         <v>0</v>
@@ -8563,7 +9148,7 @@
         <v>0</v>
       </c>
       <c r="AE66" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF66">
         <v>0</v>
@@ -8578,9 +9163,18 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>0</v>
+      </c>
+      <c r="AN66">
         <v>0</v>
       </c>
     </row>
@@ -8589,10 +9183,10 @@
         <v>26020063</v>
       </c>
       <c r="B67" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -8643,10 +9237,10 @@
         <v>0</v>
       </c>
       <c r="T67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V67">
         <v>0</v>
@@ -8661,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="Z67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA67">
         <v>0</v>
@@ -8676,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="AE67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF67">
         <v>0</v>
@@ -8691,9 +9285,18 @@
         <v>0</v>
       </c>
       <c r="AJ67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>0</v>
+      </c>
+      <c r="AN67">
         <v>0</v>
       </c>
     </row>
@@ -8702,10 +9305,10 @@
         <v>26020064</v>
       </c>
       <c r="B68" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -8756,10 +9359,10 @@
         <v>0</v>
       </c>
       <c r="T68" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U68" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V68">
         <v>0</v>
@@ -8774,7 +9377,7 @@
         <v>0</v>
       </c>
       <c r="Z68" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA68">
         <v>0</v>
@@ -8789,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="AE68" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF68">
         <v>0</v>
@@ -8801,12 +9404,21 @@
         <v>0</v>
       </c>
       <c r="AI68">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ68" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>0</v>
+      </c>
+      <c r="AN68">
         <v>0</v>
       </c>
     </row>
@@ -8815,10 +9427,10 @@
         <v>26020065</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C69" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D69">
         <v>3</v>
@@ -8869,10 +9481,10 @@
         <v>0</v>
       </c>
       <c r="T69" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U69" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V69">
         <v>0</v>
@@ -8887,7 +9499,7 @@
         <v>0</v>
       </c>
       <c r="Z69" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA69">
         <v>0</v>
@@ -8902,7 +9514,7 @@
         <v>0</v>
       </c>
       <c r="AE69" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF69">
         <v>0</v>
@@ -8914,12 +9526,21 @@
         <v>0</v>
       </c>
       <c r="AI69">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="AJ69" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK69">
+        <v>0</v>
+      </c>
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>0</v>
+      </c>
+      <c r="AN69">
         <v>0</v>
       </c>
     </row>
@@ -8928,10 +9549,10 @@
         <v>26020066</v>
       </c>
       <c r="B70" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C70" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -8982,10 +9603,10 @@
         <v>0</v>
       </c>
       <c r="T70" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U70" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V70">
         <v>0</v>
@@ -9000,7 +9621,7 @@
         <v>0</v>
       </c>
       <c r="Z70" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA70">
         <v>0</v>
@@ -9015,7 +9636,7 @@
         <v>0</v>
       </c>
       <c r="AE70" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF70">
         <v>0</v>
@@ -9030,9 +9651,18 @@
         <v>0</v>
       </c>
       <c r="AJ70" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>0</v>
+      </c>
+      <c r="AN70">
         <v>0</v>
       </c>
     </row>
@@ -9041,10 +9671,10 @@
         <v>26020067</v>
       </c>
       <c r="B71" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -9095,10 +9725,10 @@
         <v>0</v>
       </c>
       <c r="T71" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U71" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V71">
         <v>0</v>
@@ -9113,7 +9743,7 @@
         <v>0</v>
       </c>
       <c r="Z71" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA71">
         <v>0</v>
@@ -9128,7 +9758,7 @@
         <v>0</v>
       </c>
       <c r="AE71" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF71">
         <v>0</v>
@@ -9140,12 +9770,21 @@
         <v>0</v>
       </c>
       <c r="AI71">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="AJ71" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK71">
+        <v>0</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>0</v>
+      </c>
+      <c r="AN71">
         <v>0</v>
       </c>
     </row>
@@ -9154,10 +9793,10 @@
         <v>26020068</v>
       </c>
       <c r="B72" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C72" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -9208,10 +9847,10 @@
         <v>0</v>
       </c>
       <c r="T72" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U72" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V72">
         <v>0</v>
@@ -9226,7 +9865,7 @@
         <v>0</v>
       </c>
       <c r="Z72" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA72">
         <v>0</v>
@@ -9241,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="AE72" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF72">
         <v>0</v>
@@ -9253,12 +9892,21 @@
         <v>0</v>
       </c>
       <c r="AI72">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="AJ72" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK72">
+        <v>0</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>0</v>
+      </c>
+      <c r="AN72">
         <v>0</v>
       </c>
     </row>
@@ -9267,10 +9915,10 @@
         <v>26020069</v>
       </c>
       <c r="B73" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C73" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -9321,10 +9969,10 @@
         <v>0</v>
       </c>
       <c r="T73" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U73" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V73">
         <v>0</v>
@@ -9339,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="Z73" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA73">
         <v>0</v>
@@ -9354,7 +10002,7 @@
         <v>0</v>
       </c>
       <c r="AE73" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF73">
         <v>0</v>
@@ -9369,9 +10017,18 @@
         <v>0</v>
       </c>
       <c r="AJ73" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>0</v>
+      </c>
+      <c r="AN73">
         <v>0</v>
       </c>
     </row>
@@ -9380,10 +10037,10 @@
         <v>26020070</v>
       </c>
       <c r="B74" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -9434,10 +10091,10 @@
         <v>0</v>
       </c>
       <c r="T74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V74">
         <v>0</v>
@@ -9452,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="Z74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA74">
         <v>0</v>
@@ -9467,7 +10124,7 @@
         <v>0</v>
       </c>
       <c r="AE74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF74">
         <v>0</v>
@@ -9479,12 +10136,21 @@
         <v>0</v>
       </c>
       <c r="AI74">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ74" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>0</v>
+      </c>
+      <c r="AN74">
         <v>0</v>
       </c>
     </row>
@@ -9493,10 +10159,10 @@
         <v>26020071</v>
       </c>
       <c r="B75" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C75" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -9547,10 +10213,10 @@
         <v>0</v>
       </c>
       <c r="T75" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U75" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V75">
         <v>0</v>
@@ -9565,7 +10231,7 @@
         <v>0</v>
       </c>
       <c r="Z75" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA75">
         <v>0</v>
@@ -9580,7 +10246,7 @@
         <v>0</v>
       </c>
       <c r="AE75" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF75">
         <v>0</v>
@@ -9595,9 +10261,18 @@
         <v>0</v>
       </c>
       <c r="AJ75" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>0</v>
+      </c>
+      <c r="AN75">
         <v>0</v>
       </c>
     </row>
@@ -9606,10 +10281,10 @@
         <v>26020072</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -9660,10 +10335,10 @@
         <v>0</v>
       </c>
       <c r="T76" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U76" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V76">
         <v>0</v>
@@ -9678,7 +10353,7 @@
         <v>0</v>
       </c>
       <c r="Z76" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA76">
         <v>0</v>
@@ -9693,7 +10368,7 @@
         <v>0</v>
       </c>
       <c r="AE76" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF76">
         <v>0</v>
@@ -9705,12 +10380,21 @@
         <v>0</v>
       </c>
       <c r="AI76">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AJ76" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK76">
+        <v>0</v>
+      </c>
+      <c r="AL76">
+        <v>0</v>
+      </c>
+      <c r="AM76">
+        <v>0</v>
+      </c>
+      <c r="AN76">
         <v>0</v>
       </c>
     </row>
@@ -9719,10 +10403,10 @@
         <v>26020073</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C77" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D77">
         <v>3</v>
@@ -9773,10 +10457,10 @@
         <v>0</v>
       </c>
       <c r="T77" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U77" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V77">
         <v>0</v>
@@ -9791,7 +10475,7 @@
         <v>0</v>
       </c>
       <c r="Z77" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA77">
         <v>0</v>
@@ -9806,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="AE77" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF77">
         <v>0</v>
@@ -9821,9 +10505,18 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK77">
+        <v>0</v>
+      </c>
+      <c r="AL77">
+        <v>0</v>
+      </c>
+      <c r="AM77">
+        <v>0</v>
+      </c>
+      <c r="AN77">
         <v>0</v>
       </c>
     </row>
@@ -9832,10 +10525,10 @@
         <v>26020074</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C78" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -9886,10 +10579,10 @@
         <v>0</v>
       </c>
       <c r="T78" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="U78" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V78">
         <v>0</v>
@@ -9904,7 +10597,7 @@
         <v>0</v>
       </c>
       <c r="Z78" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA78">
         <v>0</v>
@@ -9919,7 +10612,7 @@
         <v>0</v>
       </c>
       <c r="AE78" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF78">
         <v>0</v>
@@ -9934,10 +10627,19 @@
         <v>0</v>
       </c>
       <c r="AJ78" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AK78">
         <v>1</v>
+      </c>
+      <c r="AL78">
+        <v>0</v>
+      </c>
+      <c r="AM78">
+        <v>0</v>
+      </c>
+      <c r="AN78">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -9945,10 +10647,10 @@
         <v>26020075</v>
       </c>
       <c r="B79" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C79" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D79">
         <v>3</v>
@@ -9999,10 +10701,10 @@
         <v>0</v>
       </c>
       <c r="T79" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U79" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V79">
         <v>0</v>
@@ -10017,7 +10719,7 @@
         <v>0</v>
       </c>
       <c r="Z79" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA79">
         <v>0</v>
@@ -10032,7 +10734,7 @@
         <v>0</v>
       </c>
       <c r="AE79" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF79">
         <v>0</v>
@@ -10044,12 +10746,21 @@
         <v>0</v>
       </c>
       <c r="AI79">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="AJ79" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK79">
+        <v>0</v>
+      </c>
+      <c r="AL79">
+        <v>0</v>
+      </c>
+      <c r="AM79">
+        <v>0</v>
+      </c>
+      <c r="AN79">
         <v>0</v>
       </c>
     </row>
@@ -10058,10 +10769,10 @@
         <v>26020076</v>
       </c>
       <c r="B80" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C80" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -10112,10 +10823,10 @@
         <v>0</v>
       </c>
       <c r="T80" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U80" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V80">
         <v>0</v>
@@ -10130,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="Z80" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA80">
         <v>0</v>
@@ -10145,7 +10856,7 @@
         <v>0</v>
       </c>
       <c r="AE80" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF80">
         <v>0</v>
@@ -10157,12 +10868,21 @@
         <v>0</v>
       </c>
       <c r="AI80">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="AJ80" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK80">
+        <v>0</v>
+      </c>
+      <c r="AL80">
+        <v>0</v>
+      </c>
+      <c r="AM80">
+        <v>0</v>
+      </c>
+      <c r="AN80">
         <v>0</v>
       </c>
     </row>
@@ -10171,10 +10891,10 @@
         <v>26020077</v>
       </c>
       <c r="B81" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -10225,10 +10945,10 @@
         <v>0</v>
       </c>
       <c r="T81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V81">
         <v>0</v>
@@ -10243,7 +10963,7 @@
         <v>0</v>
       </c>
       <c r="Z81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA81">
         <v>0</v>
@@ -10258,7 +10978,7 @@
         <v>0</v>
       </c>
       <c r="AE81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF81">
         <v>0</v>
@@ -10270,12 +10990,21 @@
         <v>0</v>
       </c>
       <c r="AI81">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="AJ81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK81">
+        <v>0</v>
+      </c>
+      <c r="AL81">
+        <v>0</v>
+      </c>
+      <c r="AM81">
+        <v>0</v>
+      </c>
+      <c r="AN81">
         <v>0</v>
       </c>
     </row>
@@ -10284,10 +11013,10 @@
         <v>26020078</v>
       </c>
       <c r="B82" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -10338,10 +11067,10 @@
         <v>0</v>
       </c>
       <c r="T82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V82">
         <v>0</v>
@@ -10356,7 +11085,7 @@
         <v>0</v>
       </c>
       <c r="Z82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA82">
         <v>0</v>
@@ -10371,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="AE82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF82">
         <v>0</v>
@@ -10386,9 +11115,18 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK82">
+        <v>0</v>
+      </c>
+      <c r="AL82">
+        <v>0</v>
+      </c>
+      <c r="AM82">
+        <v>0</v>
+      </c>
+      <c r="AN82">
         <v>0</v>
       </c>
     </row>
@@ -10397,10 +11135,10 @@
         <v>26020079</v>
       </c>
       <c r="B83" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C83" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -10451,10 +11189,10 @@
         <v>0</v>
       </c>
       <c r="T83" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U83" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V83">
         <v>0</v>
@@ -10469,7 +11207,7 @@
         <v>0</v>
       </c>
       <c r="Z83" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA83">
         <v>0</v>
@@ -10484,7 +11222,7 @@
         <v>0</v>
       </c>
       <c r="AE83" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF83">
         <v>0</v>
@@ -10499,9 +11237,18 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK83">
+        <v>0</v>
+      </c>
+      <c r="AL83">
+        <v>0</v>
+      </c>
+      <c r="AM83">
+        <v>0</v>
+      </c>
+      <c r="AN83">
         <v>0</v>
       </c>
     </row>
@@ -10510,10 +11257,10 @@
         <v>26020080</v>
       </c>
       <c r="B84" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -10564,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="T84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V84">
         <v>0</v>
@@ -10582,7 +11329,7 @@
         <v>0</v>
       </c>
       <c r="Z84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA84">
         <v>0</v>
@@ -10597,7 +11344,7 @@
         <v>0</v>
       </c>
       <c r="AE84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF84">
         <v>0</v>
@@ -10609,12 +11356,21 @@
         <v>0</v>
       </c>
       <c r="AI84">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK84">
+        <v>0</v>
+      </c>
+      <c r="AL84">
+        <v>0</v>
+      </c>
+      <c r="AM84">
+        <v>0</v>
+      </c>
+      <c r="AN84">
         <v>0</v>
       </c>
     </row>
@@ -10623,10 +11379,10 @@
         <v>26020081</v>
       </c>
       <c r="B85" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C85" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -10677,10 +11433,10 @@
         <v>0</v>
       </c>
       <c r="T85" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U85" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -10695,7 +11451,7 @@
         <v>0</v>
       </c>
       <c r="Z85" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA85">
         <v>0</v>
@@ -10710,7 +11466,7 @@
         <v>0</v>
       </c>
       <c r="AE85" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF85">
         <v>0</v>
@@ -10725,9 +11481,18 @@
         <v>0</v>
       </c>
       <c r="AJ85" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK85">
+        <v>0</v>
+      </c>
+      <c r="AL85">
+        <v>0</v>
+      </c>
+      <c r="AM85">
+        <v>0</v>
+      </c>
+      <c r="AN85">
         <v>0</v>
       </c>
     </row>
@@ -10736,10 +11501,10 @@
         <v>26020082</v>
       </c>
       <c r="B86" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C86" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -10790,10 +11555,10 @@
         <v>0</v>
       </c>
       <c r="T86" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="U86" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V86">
         <v>0</v>
@@ -10808,7 +11573,7 @@
         <v>30000</v>
       </c>
       <c r="Z86" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA86">
         <v>0</v>
@@ -10823,7 +11588,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF86">
         <v>0</v>
@@ -10838,9 +11603,18 @@
         <v>0</v>
       </c>
       <c r="AJ86" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK86">
+        <v>0</v>
+      </c>
+      <c r="AL86">
+        <v>0</v>
+      </c>
+      <c r="AM86">
+        <v>0</v>
+      </c>
+      <c r="AN86">
         <v>0</v>
       </c>
     </row>
@@ -10849,10 +11623,10 @@
         <v>26020083</v>
       </c>
       <c r="B87" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D87">
         <v>3</v>
@@ -10903,10 +11677,10 @@
         <v>0</v>
       </c>
       <c r="T87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V87">
         <v>0</v>
@@ -10921,7 +11695,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA87">
         <v>0</v>
@@ -10936,7 +11710,7 @@
         <v>0</v>
       </c>
       <c r="AE87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF87">
         <v>0</v>
@@ -10951,9 +11725,18 @@
         <v>0</v>
       </c>
       <c r="AJ87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK87">
+        <v>0</v>
+      </c>
+      <c r="AL87">
+        <v>0</v>
+      </c>
+      <c r="AM87">
+        <v>0</v>
+      </c>
+      <c r="AN87">
         <v>0</v>
       </c>
     </row>
@@ -10962,10 +11745,10 @@
         <v>26020084</v>
       </c>
       <c r="B88" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D88">
         <v>3</v>
@@ -11016,10 +11799,10 @@
         <v>0</v>
       </c>
       <c r="T88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V88">
         <v>0</v>
@@ -11034,7 +11817,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA88">
         <v>0</v>
@@ -11049,7 +11832,7 @@
         <v>0</v>
       </c>
       <c r="AE88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF88">
         <v>0</v>
@@ -11061,12 +11844,21 @@
         <v>0</v>
       </c>
       <c r="AI88">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AJ88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK88">
+        <v>0</v>
+      </c>
+      <c r="AL88">
+        <v>0</v>
+      </c>
+      <c r="AM88">
+        <v>0</v>
+      </c>
+      <c r="AN88">
         <v>0</v>
       </c>
     </row>
@@ -11075,10 +11867,10 @@
         <v>26020085</v>
       </c>
       <c r="B89" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C89" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D89">
         <v>3</v>
@@ -11129,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="T89" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U89" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V89">
         <v>0</v>
@@ -11147,7 +11939,7 @@
         <v>0</v>
       </c>
       <c r="Z89" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA89">
         <v>0</v>
@@ -11162,7 +11954,7 @@
         <v>0</v>
       </c>
       <c r="AE89" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF89">
         <v>0</v>
@@ -11174,12 +11966,21 @@
         <v>0</v>
       </c>
       <c r="AI89">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="AJ89" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK89">
+        <v>0</v>
+      </c>
+      <c r="AL89">
+        <v>0</v>
+      </c>
+      <c r="AM89">
+        <v>0</v>
+      </c>
+      <c r="AN89">
         <v>0</v>
       </c>
     </row>
@@ -11188,10 +11989,10 @@
         <v>26020086</v>
       </c>
       <c r="B90" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C90" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -11242,10 +12043,10 @@
         <v>0</v>
       </c>
       <c r="T90" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U90" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V90">
         <v>0</v>
@@ -11260,7 +12061,7 @@
         <v>0</v>
       </c>
       <c r="Z90" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA90">
         <v>0</v>
@@ -11275,7 +12076,7 @@
         <v>0</v>
       </c>
       <c r="AE90" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF90">
         <v>0</v>
@@ -11290,9 +12091,18 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK90">
+        <v>0</v>
+      </c>
+      <c r="AL90">
+        <v>0</v>
+      </c>
+      <c r="AM90">
+        <v>0</v>
+      </c>
+      <c r="AN90">
         <v>0</v>
       </c>
     </row>
@@ -11301,10 +12111,10 @@
         <v>26020087</v>
       </c>
       <c r="B91" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C91" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D91">
         <v>3</v>
@@ -11355,10 +12165,10 @@
         <v>0</v>
       </c>
       <c r="T91" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U91" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V91">
         <v>0</v>
@@ -11373,7 +12183,7 @@
         <v>0</v>
       </c>
       <c r="Z91" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA91">
         <v>0</v>
@@ -11388,7 +12198,7 @@
         <v>0</v>
       </c>
       <c r="AE91" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF91">
         <v>0</v>
@@ -11403,9 +12213,18 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK91">
+        <v>0</v>
+      </c>
+      <c r="AL91">
+        <v>0</v>
+      </c>
+      <c r="AM91">
+        <v>0</v>
+      </c>
+      <c r="AN91">
         <v>0</v>
       </c>
     </row>
@@ -11414,10 +12233,10 @@
         <v>26020088</v>
       </c>
       <c r="B92" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C92" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D92">
         <v>3</v>
@@ -11468,10 +12287,10 @@
         <v>0</v>
       </c>
       <c r="T92" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U92" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V92">
         <v>0</v>
@@ -11486,7 +12305,7 @@
         <v>0</v>
       </c>
       <c r="Z92" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA92">
         <v>0</v>
@@ -11501,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="AE92" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF92">
         <v>0</v>
@@ -11516,9 +12335,18 @@
         <v>0</v>
       </c>
       <c r="AJ92" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK92">
+        <v>0</v>
+      </c>
+      <c r="AL92">
+        <v>0</v>
+      </c>
+      <c r="AM92">
+        <v>0</v>
+      </c>
+      <c r="AN92">
         <v>0</v>
       </c>
     </row>
@@ -11527,10 +12355,10 @@
         <v>26020089</v>
       </c>
       <c r="B93" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D93">
         <v>3</v>
@@ -11581,10 +12409,10 @@
         <v>0</v>
       </c>
       <c r="T93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V93">
         <v>0</v>
@@ -11599,7 +12427,7 @@
         <v>0</v>
       </c>
       <c r="Z93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA93">
         <v>0</v>
@@ -11614,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="AE93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF93">
         <v>0</v>
@@ -11629,9 +12457,18 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK93">
+        <v>0</v>
+      </c>
+      <c r="AL93">
+        <v>0</v>
+      </c>
+      <c r="AM93">
+        <v>0</v>
+      </c>
+      <c r="AN93">
         <v>0</v>
       </c>
     </row>
@@ -11640,10 +12477,10 @@
         <v>26020090</v>
       </c>
       <c r="B94" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C94" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -11694,10 +12531,10 @@
         <v>0</v>
       </c>
       <c r="T94" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U94" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="V94">
         <v>0</v>
@@ -11712,7 +12549,7 @@
         <v>0</v>
       </c>
       <c r="Z94" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AA94">
         <v>0</v>
@@ -11727,7 +12564,7 @@
         <v>0</v>
       </c>
       <c r="AE94" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AF94">
         <v>0</v>
@@ -11742,9 +12579,18 @@
         <v>0</v>
       </c>
       <c r="AJ94" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AK94">
+        <v>0</v>
+      </c>
+      <c r="AL94">
+        <v>0</v>
+      </c>
+      <c r="AM94">
+        <v>0</v>
+      </c>
+      <c r="AN94">
         <v>0</v>
       </c>
     </row>

--- a/策划/数值文档/unit_cs-pack.xlsx
+++ b/策划/数值文档/unit_cs-pack.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
   <si>
     <t>id</t>
   </si>
@@ -136,6 +136,9 @@
     <t>jump_speed</t>
   </si>
   <si>
+    <t>homing</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -254,6 +257,18 @@
   </si>
   <si>
     <t>1=飞行单位（官方 cards_stats_characters.json 的 flying_height&gt;0）；0=地面（建筑/塔/投射物恒 0）</t>
+  </si>
+  <si>
+    <t>周期性召唤波内错开间隔 ms（官方 spawn_interval）</t>
+  </si>
+  <si>
+    <t>可跳过的水域宽度 milli-tile（官方 jump_height）</t>
+  </si>
+  <si>
+    <t>跳跃期间水平速度（格/分钟，官方 jump_speed）</t>
+  </si>
+  <si>
+    <t>1=弹道每 tick 重瞄目标（官方 cards_stats_projectile.json:homing）；非投射物行 0</t>
   </si>
   <si>
     <t>knight</t>
@@ -1256,362 +1271,383 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>41</v>
       </c>
-      <c r="D2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
         <v>41</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>41</v>
       </c>
-      <c r="V2" t="s">
-        <v>40</v>
-      </c>
-      <c r="W2" t="s">
-        <v>40</v>
-      </c>
       <c r="X2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA2" t="s">
         <v>41</v>
       </c>
-      <c r="AA2" t="s">
-        <v>40</v>
-      </c>
       <c r="AB2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AC2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AD2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AE2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF2" t="s">
         <v>41</v>
       </c>
-      <c r="AF2" t="s">
-        <v>40</v>
-      </c>
       <c r="AG2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AH2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AI2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AJ2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="s">
         <v>41</v>
       </c>
-      <c r="AK2" t="s">
-        <v>40</v>
-      </c>
       <c r="AL2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AM2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AN2" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Y3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Z3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AA3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AB3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AC3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AD3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AE3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AF3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AG3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AH3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AI3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AJ3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AK3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AL3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AM3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AN3" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AA4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AC4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AF4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AG4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AH4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AI4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AK4" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -1619,10 +1655,10 @@
         <v>26020001</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1673,10 +1709,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V5">
         <v>0</v>
@@ -1691,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="Z5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA5">
         <v>0</v>
@@ -1706,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF5">
         <v>1</v>
@@ -1721,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -1733,6 +1769,9 @@
         <v>0</v>
       </c>
       <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
         <v>0</v>
       </c>
     </row>
@@ -1741,10 +1780,10 @@
         <v>26020002</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1795,10 +1834,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="U6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V6">
         <v>0</v>
@@ -1813,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="Z6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA6">
         <v>0</v>
@@ -1828,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AF6">
         <v>2</v>
@@ -1843,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AK6">
         <v>0</v>
@@ -1855,6 +1894,9 @@
         <v>0</v>
       </c>
       <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
         <v>0</v>
       </c>
     </row>
@@ -1863,10 +1905,10 @@
         <v>26020003</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1917,10 +1959,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="U7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V7">
         <v>0</v>
@@ -1935,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA7">
         <v>0</v>
@@ -1950,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF7">
         <v>0</v>
@@ -1965,7 +2007,7 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AK7">
         <v>0</v>
@@ -1977,6 +2019,9 @@
         <v>0</v>
       </c>
       <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
         <v>0</v>
       </c>
     </row>
@@ -1985,10 +2030,10 @@
         <v>26020004</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2039,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V8">
         <v>0</v>
@@ -2057,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="Z8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA8">
         <v>0</v>
@@ -2072,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="AF8">
         <v>4</v>
@@ -2087,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="AK8">
         <v>0</v>
@@ -2099,6 +2144,9 @@
         <v>0</v>
       </c>
       <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
         <v>0</v>
       </c>
     </row>
@@ -2107,10 +2155,10 @@
         <v>26020005</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2161,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2179,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="Z9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA9">
         <v>0</v>
@@ -2194,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF9">
         <v>0</v>
@@ -2209,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="AK9">
         <v>0</v>
@@ -2221,6 +2269,9 @@
         <v>0</v>
       </c>
       <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
         <v>0</v>
       </c>
     </row>
@@ -2229,10 +2280,10 @@
         <v>26020006</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2283,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="U10" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V10">
         <v>0</v>
@@ -2301,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="Z10" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA10">
         <v>0</v>
@@ -2316,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="AF10">
         <v>3</v>
@@ -2331,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="AK10">
         <v>0</v>
@@ -2343,6 +2394,9 @@
         <v>0</v>
       </c>
       <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
         <v>0</v>
       </c>
     </row>
@@ -2351,10 +2405,10 @@
         <v>26020007</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -2405,10 +2459,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="U11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V11">
         <v>0</v>
@@ -2423,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="Z11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA11">
         <v>0</v>
@@ -2438,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF11">
         <v>0</v>
@@ -2453,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="AK11">
         <v>0</v>
@@ -2465,6 +2519,9 @@
         <v>0</v>
       </c>
       <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
         <v>0</v>
       </c>
     </row>
@@ -2473,10 +2530,10 @@
         <v>26020008</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2527,10 +2584,10 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -2545,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="Z12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA12">
         <v>0</v>
@@ -2560,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AF12">
         <v>1</v>
@@ -2575,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AK12">
         <v>0</v>
@@ -2587,6 +2644,9 @@
         <v>0</v>
       </c>
       <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
         <v>0</v>
       </c>
     </row>
@@ -2595,10 +2655,10 @@
         <v>26020009</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -2649,10 +2709,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U13" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -2667,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Z13" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA13">
         <v>0</v>
@@ -2682,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="AF13">
         <v>1</v>
@@ -2697,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="AK13">
         <v>0</v>
@@ -2709,6 +2769,9 @@
         <v>0</v>
       </c>
       <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
         <v>0</v>
       </c>
     </row>
@@ -2717,10 +2780,10 @@
         <v>26020010</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -2771,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="U14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -2789,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="Z14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA14">
         <v>0</v>
@@ -2804,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AF14">
         <v>3</v>
@@ -2819,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AK14">
         <v>1</v>
@@ -2831,6 +2894,9 @@
         <v>0</v>
       </c>
       <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
         <v>0</v>
       </c>
     </row>
@@ -2839,10 +2905,10 @@
         <v>26020011</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -2893,10 +2959,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="U15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -2911,7 +2977,7 @@
         <v>0</v>
       </c>
       <c r="Z15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA15">
         <v>0</v>
@@ -2926,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF15">
         <v>0</v>
@@ -2941,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AK15">
         <v>1</v>
@@ -2953,6 +3019,9 @@
         <v>0</v>
       </c>
       <c r="AN15">
+        <v>0</v>
+      </c>
+      <c r="AO15">
         <v>0</v>
       </c>
     </row>
@@ -2961,10 +3030,10 @@
         <v>26020012</v>
       </c>
       <c r="B16" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -3015,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="U16" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -3033,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="Z16" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA16">
         <v>0</v>
@@ -3048,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="AF16">
         <v>6</v>
@@ -3063,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="AK16">
         <v>1</v>
@@ -3075,6 +3144,9 @@
         <v>0</v>
       </c>
       <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AO16">
         <v>0</v>
       </c>
     </row>
@@ -3083,10 +3155,10 @@
         <v>26020013</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -3137,10 +3209,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U17" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -3155,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="Z17" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA17">
         <v>0</v>
@@ -3170,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="AF17">
         <v>1</v>
@@ -3185,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AK17">
         <v>1</v>
@@ -3197,6 +3269,9 @@
         <v>0</v>
       </c>
       <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
         <v>0</v>
       </c>
     </row>
@@ -3205,10 +3280,10 @@
         <v>26020014</v>
       </c>
       <c r="B18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -3259,10 +3334,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="U18" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -3277,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="Z18" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AA18">
         <v>4</v>
@@ -3292,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="AF18">
         <v>1</v>
@@ -3307,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="AK18">
         <v>0</v>
@@ -3319,6 +3394,9 @@
         <v>0</v>
       </c>
       <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
         <v>0</v>
       </c>
     </row>
@@ -3327,10 +3405,10 @@
         <v>26020015</v>
       </c>
       <c r="B19" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -3381,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U19" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -3399,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="Z19" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA19">
         <v>0</v>
@@ -3414,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AF19">
         <v>5</v>
@@ -3429,7 +3507,7 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AK19">
         <v>0</v>
@@ -3441,6 +3519,9 @@
         <v>0</v>
       </c>
       <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
         <v>0</v>
       </c>
     </row>
@@ -3449,10 +3530,10 @@
         <v>26020016</v>
       </c>
       <c r="B20" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -3503,10 +3584,10 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -3521,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="Z20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA20">
         <v>0</v>
@@ -3536,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF20">
         <v>0</v>
@@ -3551,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="AK20">
         <v>0</v>
@@ -3563,6 +3644,9 @@
         <v>0</v>
       </c>
       <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
         <v>0</v>
       </c>
     </row>
@@ -3571,10 +3655,10 @@
         <v>26020017</v>
       </c>
       <c r="B21" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -3625,10 +3709,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U21" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -3643,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="Z21" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA21">
         <v>0</v>
@@ -3658,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AF21">
         <v>3</v>
@@ -3673,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="AK21">
         <v>0</v>
@@ -3685,6 +3769,9 @@
         <v>0</v>
       </c>
       <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
         <v>0</v>
       </c>
     </row>
@@ -3693,10 +3780,10 @@
         <v>26020018</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3747,10 +3834,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U22" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V22">
         <v>0</v>
@@ -3765,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="Z22" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA22">
         <v>0</v>
@@ -3780,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -3795,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="AK22">
         <v>0</v>
@@ -3807,6 +3894,9 @@
         <v>0</v>
       </c>
       <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
         <v>0</v>
       </c>
     </row>
@@ -3815,10 +3905,10 @@
         <v>26020019</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -3869,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U23" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -3887,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="Z23" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA23">
         <v>0</v>
@@ -3902,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AF23">
         <v>15</v>
@@ -3917,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="AK23">
         <v>0</v>
@@ -3929,6 +4019,9 @@
         <v>0</v>
       </c>
       <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
         <v>0</v>
       </c>
     </row>
@@ -3937,10 +4030,10 @@
         <v>26020020</v>
       </c>
       <c r="B24" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3991,10 +4084,10 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -4009,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="Z24" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA24">
         <v>0</v>
@@ -4024,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AF24">
         <v>1</v>
@@ -4039,7 +4132,7 @@
         <v>2000</v>
       </c>
       <c r="AJ24" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AK24">
         <v>0</v>
@@ -4051,6 +4144,9 @@
         <v>0</v>
       </c>
       <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
         <v>0</v>
       </c>
     </row>
@@ -4059,10 +4155,10 @@
         <v>26020021</v>
       </c>
       <c r="B25" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4113,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="U25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V25">
         <v>0</v>
@@ -4131,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="Z25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA25">
         <v>0</v>
@@ -4146,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="AF25">
         <v>1</v>
@@ -4161,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AK25">
         <v>0</v>
@@ -4173,6 +4269,9 @@
         <v>0</v>
       </c>
       <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AO25">
         <v>0</v>
       </c>
     </row>
@@ -4181,10 +4280,10 @@
         <v>26020022</v>
       </c>
       <c r="B26" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C26" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4235,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="U26" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -4253,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA26">
         <v>0</v>
@@ -4268,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AF26">
         <v>1</v>
@@ -4283,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK26">
         <v>0</v>
@@ -4295,6 +4394,9 @@
         <v>0</v>
       </c>
       <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AO26">
         <v>0</v>
       </c>
     </row>
@@ -4303,10 +4405,10 @@
         <v>26020023</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4357,10 +4459,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="U27" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -4375,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="Z27" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA27">
         <v>0</v>
@@ -4390,7 +4492,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AF27">
         <v>1</v>
@@ -4405,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AK27">
         <v>1</v>
@@ -4417,6 +4519,9 @@
         <v>0</v>
       </c>
       <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
         <v>0</v>
       </c>
     </row>
@@ -4425,10 +4530,10 @@
         <v>26020024</v>
       </c>
       <c r="B28" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C28" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -4479,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U28" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -4497,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="Z28" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -4512,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AF28">
         <v>1</v>
@@ -4527,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AK28">
         <v>0</v>
@@ -4540,6 +4645,9 @@
       </c>
       <c r="AN28">
         <v>160</v>
+      </c>
+      <c r="AO28">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4547,10 +4655,10 @@
         <v>26020025</v>
       </c>
       <c r="B29" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C29" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -4601,10 +4709,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="U29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -4619,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="Z29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA29">
         <v>0</v>
@@ -4634,7 +4742,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AF29">
         <v>1</v>
@@ -4649,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AK29">
         <v>0</v>
@@ -4661,6 +4769,9 @@
         <v>0</v>
       </c>
       <c r="AN29">
+        <v>0</v>
+      </c>
+      <c r="AO29">
         <v>0</v>
       </c>
     </row>
@@ -4669,10 +4780,10 @@
         <v>26020026</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -4723,10 +4834,10 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U30" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -4741,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="Z30" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -4756,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AF30">
         <v>1</v>
@@ -4771,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AK30">
         <v>0</v>
@@ -4783,6 +4894,9 @@
         <v>0</v>
       </c>
       <c r="AN30">
+        <v>0</v>
+      </c>
+      <c r="AO30">
         <v>0</v>
       </c>
     </row>
@@ -4791,10 +4905,10 @@
         <v>26020027</v>
       </c>
       <c r="B31" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C31" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -4845,10 +4959,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U31" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="V31">
         <v>1</v>
@@ -4863,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="Z31" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA31">
         <v>0</v>
@@ -4878,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AF31">
         <v>1</v>
@@ -4893,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AK31">
         <v>0</v>
@@ -4905,6 +5019,9 @@
         <v>0</v>
       </c>
       <c r="AN31">
+        <v>0</v>
+      </c>
+      <c r="AO31">
         <v>0</v>
       </c>
     </row>
@@ -4913,10 +5030,10 @@
         <v>26020028</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C32" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -4967,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U32" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -4985,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="Z32" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA32">
         <v>0</v>
@@ -5000,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AF32">
         <v>1</v>
@@ -5015,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AK32">
         <v>0</v>
@@ -5028,6 +5145,9 @@
       </c>
       <c r="AN32">
         <v>160</v>
+      </c>
+      <c r="AO32">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -5035,10 +5155,10 @@
         <v>26020029</v>
       </c>
       <c r="B33" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -5089,10 +5209,10 @@
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="U33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V33">
         <v>0</v>
@@ -5107,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="Z33" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA33">
         <v>0</v>
@@ -5122,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AF33">
         <v>1</v>
@@ -5137,7 +5257,7 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AK33">
         <v>0</v>
@@ -5149,6 +5269,9 @@
         <v>0</v>
       </c>
       <c r="AN33">
+        <v>0</v>
+      </c>
+      <c r="AO33">
         <v>0</v>
       </c>
     </row>
@@ -5157,10 +5280,10 @@
         <v>26020030</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C34" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -5211,10 +5334,10 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="U34" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V34">
         <v>0</v>
@@ -5229,7 +5352,7 @@
         <v>0</v>
       </c>
       <c r="Z34" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA34">
         <v>0</v>
@@ -5244,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="AF34">
         <v>1</v>
@@ -5259,7 +5382,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="AK34">
         <v>0</v>
@@ -5271,6 +5394,9 @@
         <v>0</v>
       </c>
       <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
         <v>0</v>
       </c>
     </row>
@@ -5279,10 +5405,10 @@
         <v>26020031</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -5333,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="U35" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -5351,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="Z35" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA35">
         <v>0</v>
@@ -5366,7 +5492,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="AF35">
         <v>1</v>
@@ -5381,7 +5507,7 @@
         <v>2500</v>
       </c>
       <c r="AJ35" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="AK35">
         <v>0</v>
@@ -5393,6 +5519,9 @@
         <v>0</v>
       </c>
       <c r="AN35">
+        <v>0</v>
+      </c>
+      <c r="AO35">
         <v>0</v>
       </c>
     </row>
@@ -5401,10 +5530,10 @@
         <v>26020032</v>
       </c>
       <c r="B36" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -5455,10 +5584,10 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U36" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V36">
         <v>0</v>
@@ -5473,7 +5602,7 @@
         <v>0</v>
       </c>
       <c r="Z36" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA36">
         <v>0</v>
@@ -5488,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AF36">
         <v>1</v>
@@ -5503,7 +5632,7 @@
         <v>1100</v>
       </c>
       <c r="AJ36" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AK36">
         <v>0</v>
@@ -5516,6 +5645,9 @@
       </c>
       <c r="AN36">
         <v>160</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -5523,10 +5655,10 @@
         <v>26020033</v>
       </c>
       <c r="B37" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -5577,10 +5709,10 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="U37" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="V37">
         <v>6</v>
@@ -5595,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="Z37" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA37">
         <v>0</v>
@@ -5610,7 +5742,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="AF37">
         <v>1</v>
@@ -5625,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="AK37">
         <v>1</v>
@@ -5637,6 +5769,9 @@
         <v>0</v>
       </c>
       <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
         <v>0</v>
       </c>
     </row>
@@ -5645,10 +5780,10 @@
         <v>26020034</v>
       </c>
       <c r="B38" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -5699,10 +5834,10 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="U38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -5717,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="Z38" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA38">
         <v>0</v>
@@ -5732,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AF38">
         <v>1</v>
@@ -5747,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AK38">
         <v>0</v>
@@ -5759,6 +5894,9 @@
         <v>0</v>
       </c>
       <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
         <v>0</v>
       </c>
     </row>
@@ -5767,10 +5905,10 @@
         <v>26020035</v>
       </c>
       <c r="B39" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C39" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -5821,10 +5959,10 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="U39" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -5839,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="Z39" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA39">
         <v>0</v>
@@ -5854,7 +5992,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="AF39">
         <v>1</v>
@@ -5869,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="AK39">
         <v>0</v>
@@ -5881,6 +6019,9 @@
         <v>0</v>
       </c>
       <c r="AN39">
+        <v>0</v>
+      </c>
+      <c r="AO39">
         <v>0</v>
       </c>
     </row>
@@ -5889,10 +6030,10 @@
         <v>26020036</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C40" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -5943,10 +6084,10 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U40" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -5961,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="Z40" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA40">
         <v>0</v>
@@ -5976,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="AF40">
         <v>1</v>
@@ -5991,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="AK40">
         <v>0</v>
@@ -6003,6 +6144,9 @@
         <v>0</v>
       </c>
       <c r="AN40">
+        <v>0</v>
+      </c>
+      <c r="AO40">
         <v>0</v>
       </c>
     </row>
@@ -6011,10 +6155,10 @@
         <v>26020037</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -6065,10 +6209,10 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="U41" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -6083,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="Z41" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA41">
         <v>0</v>
@@ -6098,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AF41">
         <v>1</v>
@@ -6113,7 +6257,7 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AK41">
         <v>0</v>
@@ -6125,6 +6269,9 @@
         <v>0</v>
       </c>
       <c r="AN41">
+        <v>0</v>
+      </c>
+      <c r="AO41">
         <v>0</v>
       </c>
     </row>
@@ -6133,10 +6280,10 @@
         <v>26020038</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C42" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -6187,10 +6334,10 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U42" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="V42">
         <v>2</v>
@@ -6205,7 +6352,7 @@
         <v>0</v>
       </c>
       <c r="Z42" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA42">
         <v>0</v>
@@ -6220,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AF42">
         <v>1</v>
@@ -6235,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AK42">
         <v>0</v>
@@ -6248,6 +6395,9 @@
       </c>
       <c r="AN42">
         <v>160</v>
+      </c>
+      <c r="AO42">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -6255,10 +6405,10 @@
         <v>26020039</v>
       </c>
       <c r="B43" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C43" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -6309,10 +6459,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="U43" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -6327,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="Z43" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA43">
         <v>0</v>
@@ -6342,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AF43">
         <v>1</v>
@@ -6357,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="AK43">
         <v>1</v>
@@ -6369,6 +6519,9 @@
         <v>0</v>
       </c>
       <c r="AN43">
+        <v>0</v>
+      </c>
+      <c r="AO43">
         <v>0</v>
       </c>
     </row>
@@ -6377,10 +6530,10 @@
         <v>26020040</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -6431,10 +6584,10 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="U44" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V44">
         <v>0</v>
@@ -6449,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="Z44" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -6464,7 +6617,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AF44">
         <v>1</v>
@@ -6479,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="AK44">
         <v>0</v>
@@ -6491,6 +6644,9 @@
         <v>0</v>
       </c>
       <c r="AN44">
+        <v>0</v>
+      </c>
+      <c r="AO44">
         <v>0</v>
       </c>
     </row>
@@ -6499,10 +6655,10 @@
         <v>26020041</v>
       </c>
       <c r="B45" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C45" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -6553,10 +6709,10 @@
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U45" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V45">
         <v>0</v>
@@ -6571,7 +6727,7 @@
         <v>0</v>
       </c>
       <c r="Z45" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA45">
         <v>0</v>
@@ -6586,7 +6742,7 @@
         <v>0</v>
       </c>
       <c r="AE45" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="AF45">
         <v>1</v>
@@ -6601,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AK45">
         <v>0</v>
@@ -6613,6 +6769,9 @@
         <v>0</v>
       </c>
       <c r="AN45">
+        <v>0</v>
+      </c>
+      <c r="AO45">
         <v>0</v>
       </c>
     </row>
@@ -6621,10 +6780,10 @@
         <v>26020042</v>
       </c>
       <c r="B46" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C46" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -6675,10 +6834,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="U46" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V46">
         <v>0</v>
@@ -6693,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="Z46" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA46">
         <v>0</v>
@@ -6708,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="AE46" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="AF46">
         <v>1</v>
@@ -6723,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AK46">
         <v>0</v>
@@ -6735,6 +6894,9 @@
         <v>0</v>
       </c>
       <c r="AN46">
+        <v>0</v>
+      </c>
+      <c r="AO46">
         <v>0</v>
       </c>
     </row>
@@ -6743,10 +6905,10 @@
         <v>26020043</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C47" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -6797,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U47" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V47">
         <v>0</v>
@@ -6815,7 +6977,7 @@
         <v>0</v>
       </c>
       <c r="Z47" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA47">
         <v>0</v>
@@ -6830,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="AE47" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AF47">
         <v>1</v>
@@ -6845,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="AK47">
         <v>0</v>
@@ -6857,6 +7019,9 @@
         <v>0</v>
       </c>
       <c r="AN47">
+        <v>0</v>
+      </c>
+      <c r="AO47">
         <v>0</v>
       </c>
     </row>
@@ -6865,10 +7030,10 @@
         <v>26020044</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C48" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -6919,10 +7084,10 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U48" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V48">
         <v>0</v>
@@ -6937,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="Z48" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA48">
         <v>0</v>
@@ -6952,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="AE48" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="AF48">
         <v>5</v>
@@ -6967,7 +7132,7 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="AK48">
         <v>1</v>
@@ -6979,6 +7144,9 @@
         <v>0</v>
       </c>
       <c r="AN48">
+        <v>0</v>
+      </c>
+      <c r="AO48">
         <v>0</v>
       </c>
     </row>
@@ -6987,10 +7155,10 @@
         <v>26020045</v>
       </c>
       <c r="B49" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -7041,10 +7209,10 @@
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U49" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V49">
         <v>0</v>
@@ -7059,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="Z49" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA49">
         <v>0</v>
@@ -7074,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="AE49" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF49">
         <v>0</v>
@@ -7089,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK49">
         <v>1</v>
@@ -7101,6 +7269,9 @@
         <v>0</v>
       </c>
       <c r="AN49">
+        <v>0</v>
+      </c>
+      <c r="AO49">
         <v>0</v>
       </c>
     </row>
@@ -7109,10 +7280,10 @@
         <v>26020046</v>
       </c>
       <c r="B50" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C50" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -7163,10 +7334,10 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U50" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V50">
         <v>0</v>
@@ -7181,7 +7352,7 @@
         <v>0</v>
       </c>
       <c r="Z50" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA50">
         <v>1</v>
@@ -7196,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="AE50" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AF50">
         <v>1</v>
@@ -7211,7 +7382,7 @@
         <v>1300</v>
       </c>
       <c r="AJ50" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AK50">
         <v>0</v>
@@ -7223,6 +7394,9 @@
         <v>0</v>
       </c>
       <c r="AN50">
+        <v>0</v>
+      </c>
+      <c r="AO50">
         <v>0</v>
       </c>
     </row>
@@ -7231,10 +7405,10 @@
         <v>26020047</v>
       </c>
       <c r="B51" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -7285,10 +7459,10 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="U51" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="V51">
         <v>1</v>
@@ -7303,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="Z51" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA51">
         <v>0</v>
@@ -7318,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="AE51" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AF51">
         <v>1</v>
@@ -7333,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AK51">
         <v>0</v>
@@ -7345,6 +7519,9 @@
         <v>0</v>
       </c>
       <c r="AN51">
+        <v>0</v>
+      </c>
+      <c r="AO51">
         <v>0</v>
       </c>
     </row>
@@ -7353,10 +7530,10 @@
         <v>26020048</v>
       </c>
       <c r="B52" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C52" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -7407,10 +7584,10 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="U52" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -7425,7 +7602,7 @@
         <v>30000</v>
       </c>
       <c r="Z52" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA52">
         <v>0</v>
@@ -7440,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="AE52" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF52">
         <v>0</v>
@@ -7455,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AK52">
         <v>0</v>
@@ -7467,6 +7644,9 @@
         <v>0</v>
       </c>
       <c r="AN52">
+        <v>0</v>
+      </c>
+      <c r="AO52">
         <v>0</v>
       </c>
     </row>
@@ -7475,10 +7655,10 @@
         <v>26020049</v>
       </c>
       <c r="B53" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C53" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -7529,10 +7709,10 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U53" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="V53">
         <v>1</v>
@@ -7547,7 +7727,7 @@
         <v>29000</v>
       </c>
       <c r="Z53" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="AA53">
         <v>3</v>
@@ -7562,7 +7742,7 @@
         <v>0</v>
       </c>
       <c r="AE53" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF53">
         <v>0</v>
@@ -7577,7 +7757,7 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AK53">
         <v>0</v>
@@ -7589,6 +7769,9 @@
         <v>0</v>
       </c>
       <c r="AN53">
+        <v>0</v>
+      </c>
+      <c r="AO53">
         <v>0</v>
       </c>
     </row>
@@ -7597,10 +7780,10 @@
         <v>26020050</v>
       </c>
       <c r="B54" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C54" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -7651,10 +7834,10 @@
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="U54" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V54">
         <v>0</v>
@@ -7669,7 +7852,7 @@
         <v>30000</v>
       </c>
       <c r="Z54" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA54">
         <v>0</v>
@@ -7684,7 +7867,7 @@
         <v>0</v>
       </c>
       <c r="AE54" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF54">
         <v>0</v>
@@ -7699,7 +7882,7 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="AK54">
         <v>0</v>
@@ -7711,6 +7894,9 @@
         <v>0</v>
       </c>
       <c r="AN54">
+        <v>0</v>
+      </c>
+      <c r="AO54">
         <v>0</v>
       </c>
     </row>
@@ -7719,10 +7905,10 @@
         <v>26020051</v>
       </c>
       <c r="B55" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -7773,10 +7959,10 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U55" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V55">
         <v>0</v>
@@ -7791,7 +7977,7 @@
         <v>30000</v>
       </c>
       <c r="Z55" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA55">
         <v>0</v>
@@ -7806,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="AE55" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF55">
         <v>0</v>
@@ -7821,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="AJ55" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AK55">
         <v>0</v>
@@ -7833,6 +8019,9 @@
         <v>0</v>
       </c>
       <c r="AN55">
+        <v>0</v>
+      </c>
+      <c r="AO55">
         <v>0</v>
       </c>
     </row>
@@ -7841,10 +8030,10 @@
         <v>26020052</v>
       </c>
       <c r="B56" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C56" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -7895,10 +8084,10 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="U56" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="V56">
         <v>1</v>
@@ -7913,7 +8102,7 @@
         <v>30000</v>
       </c>
       <c r="Z56" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA56">
         <v>0</v>
@@ -7928,7 +8117,7 @@
         <v>0</v>
       </c>
       <c r="AE56" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF56">
         <v>0</v>
@@ -7943,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="AJ56" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AK56">
         <v>0</v>
@@ -7955,6 +8144,9 @@
         <v>0</v>
       </c>
       <c r="AN56">
+        <v>0</v>
+      </c>
+      <c r="AO56">
         <v>0</v>
       </c>
     </row>
@@ -7963,10 +8155,10 @@
         <v>26020053</v>
       </c>
       <c r="B57" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C57" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -8017,10 +8209,10 @@
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U57" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="V57">
         <v>1</v>
@@ -8035,7 +8227,7 @@
         <v>30000</v>
       </c>
       <c r="Z57" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="AA57">
         <v>3</v>
@@ -8050,7 +8242,7 @@
         <v>0</v>
       </c>
       <c r="AE57" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF57">
         <v>0</v>
@@ -8065,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AK57">
         <v>0</v>
@@ -8077,6 +8269,9 @@
         <v>0</v>
       </c>
       <c r="AN57">
+        <v>0</v>
+      </c>
+      <c r="AO57">
         <v>0</v>
       </c>
     </row>
@@ -8085,10 +8280,10 @@
         <v>26020054</v>
       </c>
       <c r="B58" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C58" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -8139,10 +8334,10 @@
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U58" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V58">
         <v>0</v>
@@ -8157,7 +8352,7 @@
         <v>30000</v>
       </c>
       <c r="Z58" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA58">
         <v>0</v>
@@ -8172,7 +8367,7 @@
         <v>0</v>
       </c>
       <c r="AE58" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF58">
         <v>0</v>
@@ -8187,7 +8382,7 @@
         <v>0</v>
       </c>
       <c r="AJ58" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AK58">
         <v>0</v>
@@ -8199,6 +8394,9 @@
         <v>0</v>
       </c>
       <c r="AN58">
+        <v>0</v>
+      </c>
+      <c r="AO58">
         <v>0</v>
       </c>
     </row>
@@ -8207,10 +8405,10 @@
         <v>26020055</v>
       </c>
       <c r="B59" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C59" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -8261,10 +8459,10 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U59" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V59">
         <v>0</v>
@@ -8279,7 +8477,7 @@
         <v>65000</v>
       </c>
       <c r="Z59" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA59">
         <v>0</v>
@@ -8294,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="AE59" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF59">
         <v>0</v>
@@ -8309,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AK59">
         <v>0</v>
@@ -8321,6 +8519,9 @@
         <v>0</v>
       </c>
       <c r="AN59">
+        <v>0</v>
+      </c>
+      <c r="AO59">
         <v>0</v>
       </c>
     </row>
@@ -8329,10 +8530,10 @@
         <v>26020056</v>
       </c>
       <c r="B60" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C60" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -8383,10 +8584,10 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="U60" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V60">
         <v>0</v>
@@ -8401,7 +8602,7 @@
         <v>30000</v>
       </c>
       <c r="Z60" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA60">
         <v>0</v>
@@ -8416,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AE60" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF60">
         <v>0</v>
@@ -8431,7 +8632,7 @@
         <v>0</v>
       </c>
       <c r="AJ60" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AK60">
         <v>0</v>
@@ -8443,6 +8644,9 @@
         <v>0</v>
       </c>
       <c r="AN60">
+        <v>0</v>
+      </c>
+      <c r="AO60">
         <v>0</v>
       </c>
     </row>
@@ -8451,10 +8655,10 @@
         <v>26020057</v>
       </c>
       <c r="B61" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C61" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -8505,10 +8709,10 @@
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="V61">
         <v>4</v>
@@ -8523,7 +8727,7 @@
         <v>30000</v>
       </c>
       <c r="Z61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="AA61">
         <v>2</v>
@@ -8538,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="AE61" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF61">
         <v>0</v>
@@ -8553,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AK61">
         <v>0</v>
@@ -8565,6 +8769,9 @@
         <v>0</v>
       </c>
       <c r="AN61">
+        <v>0</v>
+      </c>
+      <c r="AO61">
         <v>0</v>
       </c>
     </row>
@@ -8573,10 +8780,10 @@
         <v>26020058</v>
       </c>
       <c r="B62" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C62" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -8627,10 +8834,10 @@
         <v>0</v>
       </c>
       <c r="T62" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="U62" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V62">
         <v>0</v>
@@ -8645,7 +8852,7 @@
         <v>0</v>
       </c>
       <c r="Z62" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA62">
         <v>0</v>
@@ -8660,7 +8867,7 @@
         <v>0</v>
       </c>
       <c r="AE62" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF62">
         <v>0</v>
@@ -8675,7 +8882,7 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AK62">
         <v>0</v>
@@ -8687,6 +8894,9 @@
         <v>0</v>
       </c>
       <c r="AN62">
+        <v>0</v>
+      </c>
+      <c r="AO62">
         <v>0</v>
       </c>
     </row>
@@ -8695,10 +8905,10 @@
         <v>26020059</v>
       </c>
       <c r="B63" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C63" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -8749,10 +8959,10 @@
         <v>0</v>
       </c>
       <c r="T63" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="U63" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V63">
         <v>0</v>
@@ -8767,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="Z63" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA63">
         <v>0</v>
@@ -8782,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="AE63" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF63">
         <v>0</v>
@@ -8797,7 +9007,7 @@
         <v>0</v>
       </c>
       <c r="AJ63" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AK63">
         <v>0</v>
@@ -8809,6 +9019,9 @@
         <v>0</v>
       </c>
       <c r="AN63">
+        <v>0</v>
+      </c>
+      <c r="AO63">
         <v>0</v>
       </c>
     </row>
@@ -8817,10 +9030,10 @@
         <v>26020060</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C64" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -8871,10 +9084,10 @@
         <v>0</v>
       </c>
       <c r="T64" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U64" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V64">
         <v>0</v>
@@ -8889,7 +9102,7 @@
         <v>0</v>
       </c>
       <c r="Z64" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA64">
         <v>0</v>
@@ -8904,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="AE64" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF64">
         <v>0</v>
@@ -8919,7 +9132,7 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK64">
         <v>0</v>
@@ -8932,6 +9145,9 @@
       </c>
       <c r="AN64">
         <v>0</v>
+      </c>
+      <c r="AO64">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -8939,10 +9155,10 @@
         <v>26020061</v>
       </c>
       <c r="B65" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C65" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D65">
         <v>3</v>
@@ -8993,10 +9209,10 @@
         <v>0</v>
       </c>
       <c r="T65" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U65" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -9011,7 +9227,7 @@
         <v>0</v>
       </c>
       <c r="Z65" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA65">
         <v>0</v>
@@ -9026,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="AE65" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF65">
         <v>0</v>
@@ -9041,7 +9257,7 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK65">
         <v>0</v>
@@ -9054,6 +9270,9 @@
       </c>
       <c r="AN65">
         <v>0</v>
+      </c>
+      <c r="AO65">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -9061,10 +9280,10 @@
         <v>26020062</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C66" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -9115,10 +9334,10 @@
         <v>0</v>
       </c>
       <c r="T66" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U66" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V66">
         <v>0</v>
@@ -9133,7 +9352,7 @@
         <v>0</v>
       </c>
       <c r="Z66" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA66">
         <v>0</v>
@@ -9148,7 +9367,7 @@
         <v>0</v>
       </c>
       <c r="AE66" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF66">
         <v>0</v>
@@ -9163,7 +9382,7 @@
         <v>0</v>
       </c>
       <c r="AJ66" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK66">
         <v>0</v>
@@ -9176,6 +9395,9 @@
       </c>
       <c r="AN66">
         <v>0</v>
+      </c>
+      <c r="AO66">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -9183,10 +9405,10 @@
         <v>26020063</v>
       </c>
       <c r="B67" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -9237,10 +9459,10 @@
         <v>0</v>
       </c>
       <c r="T67" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U67" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V67">
         <v>0</v>
@@ -9255,7 +9477,7 @@
         <v>0</v>
       </c>
       <c r="Z67" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA67">
         <v>0</v>
@@ -9270,7 +9492,7 @@
         <v>0</v>
       </c>
       <c r="AE67" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF67">
         <v>0</v>
@@ -9285,7 +9507,7 @@
         <v>0</v>
       </c>
       <c r="AJ67" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK67">
         <v>0</v>
@@ -9297,6 +9519,9 @@
         <v>0</v>
       </c>
       <c r="AN67">
+        <v>0</v>
+      </c>
+      <c r="AO67">
         <v>0</v>
       </c>
     </row>
@@ -9305,10 +9530,10 @@
         <v>26020064</v>
       </c>
       <c r="B68" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -9359,10 +9584,10 @@
         <v>0</v>
       </c>
       <c r="T68" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U68" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V68">
         <v>0</v>
@@ -9377,7 +9602,7 @@
         <v>0</v>
       </c>
       <c r="Z68" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA68">
         <v>0</v>
@@ -9392,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="AE68" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF68">
         <v>0</v>
@@ -9407,7 +9632,7 @@
         <v>1000</v>
       </c>
       <c r="AJ68" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK68">
         <v>0</v>
@@ -9420,6 +9645,9 @@
       </c>
       <c r="AN68">
         <v>0</v>
+      </c>
+      <c r="AO68">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -9427,10 +9655,10 @@
         <v>26020065</v>
       </c>
       <c r="B69" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D69">
         <v>3</v>
@@ -9481,10 +9709,10 @@
         <v>0</v>
       </c>
       <c r="T69" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U69" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V69">
         <v>0</v>
@@ -9499,7 +9727,7 @@
         <v>0</v>
       </c>
       <c r="Z69" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA69">
         <v>0</v>
@@ -9514,7 +9742,7 @@
         <v>0</v>
       </c>
       <c r="AE69" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF69">
         <v>0</v>
@@ -9529,7 +9757,7 @@
         <v>1500</v>
       </c>
       <c r="AJ69" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK69">
         <v>0</v>
@@ -9541,6 +9769,9 @@
         <v>0</v>
       </c>
       <c r="AN69">
+        <v>0</v>
+      </c>
+      <c r="AO69">
         <v>0</v>
       </c>
     </row>
@@ -9549,10 +9780,10 @@
         <v>26020066</v>
       </c>
       <c r="B70" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C70" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -9603,10 +9834,10 @@
         <v>0</v>
       </c>
       <c r="T70" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U70" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V70">
         <v>0</v>
@@ -9621,7 +9852,7 @@
         <v>0</v>
       </c>
       <c r="Z70" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA70">
         <v>0</v>
@@ -9636,7 +9867,7 @@
         <v>0</v>
       </c>
       <c r="AE70" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF70">
         <v>0</v>
@@ -9651,7 +9882,7 @@
         <v>0</v>
       </c>
       <c r="AJ70" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK70">
         <v>0</v>
@@ -9664,6 +9895,9 @@
       </c>
       <c r="AN70">
         <v>0</v>
+      </c>
+      <c r="AO70">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -9671,10 +9905,10 @@
         <v>26020067</v>
       </c>
       <c r="B71" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C71" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -9725,10 +9959,10 @@
         <v>0</v>
       </c>
       <c r="T71" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U71" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V71">
         <v>0</v>
@@ -9743,7 +9977,7 @@
         <v>0</v>
       </c>
       <c r="Z71" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA71">
         <v>0</v>
@@ -9758,7 +9992,7 @@
         <v>0</v>
       </c>
       <c r="AE71" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF71">
         <v>0</v>
@@ -9773,7 +10007,7 @@
         <v>1200</v>
       </c>
       <c r="AJ71" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK71">
         <v>0</v>
@@ -9786,6 +10020,9 @@
       </c>
       <c r="AN71">
         <v>0</v>
+      </c>
+      <c r="AO71">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -9793,10 +10030,10 @@
         <v>26020068</v>
       </c>
       <c r="B72" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C72" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -9847,10 +10084,10 @@
         <v>0</v>
       </c>
       <c r="T72" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U72" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V72">
         <v>0</v>
@@ -9865,7 +10102,7 @@
         <v>0</v>
       </c>
       <c r="Z72" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA72">
         <v>0</v>
@@ -9880,7 +10117,7 @@
         <v>0</v>
       </c>
       <c r="AE72" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF72">
         <v>0</v>
@@ -9895,7 +10132,7 @@
         <v>1500</v>
       </c>
       <c r="AJ72" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK72">
         <v>0</v>
@@ -9908,6 +10145,9 @@
       </c>
       <c r="AN72">
         <v>0</v>
+      </c>
+      <c r="AO72">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -9915,10 +10155,10 @@
         <v>26020069</v>
       </c>
       <c r="B73" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C73" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -9969,10 +10209,10 @@
         <v>0</v>
       </c>
       <c r="T73" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U73" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V73">
         <v>0</v>
@@ -9987,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="Z73" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA73">
         <v>0</v>
@@ -10002,7 +10242,7 @@
         <v>0</v>
       </c>
       <c r="AE73" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF73">
         <v>0</v>
@@ -10017,7 +10257,7 @@
         <v>0</v>
       </c>
       <c r="AJ73" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK73">
         <v>0</v>
@@ -10029,6 +10269,9 @@
         <v>0</v>
       </c>
       <c r="AN73">
+        <v>0</v>
+      </c>
+      <c r="AO73">
         <v>0</v>
       </c>
     </row>
@@ -10037,10 +10280,10 @@
         <v>26020070</v>
       </c>
       <c r="B74" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C74" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -10091,10 +10334,10 @@
         <v>0</v>
       </c>
       <c r="T74" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U74" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V74">
         <v>0</v>
@@ -10109,7 +10352,7 @@
         <v>0</v>
       </c>
       <c r="Z74" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA74">
         <v>0</v>
@@ -10124,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="AE74" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF74">
         <v>0</v>
@@ -10139,7 +10382,7 @@
         <v>1000</v>
       </c>
       <c r="AJ74" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK74">
         <v>0</v>
@@ -10152,6 +10395,9 @@
       </c>
       <c r="AN74">
         <v>0</v>
+      </c>
+      <c r="AO74">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -10159,10 +10405,10 @@
         <v>26020071</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C75" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -10213,10 +10459,10 @@
         <v>0</v>
       </c>
       <c r="T75" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U75" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V75">
         <v>0</v>
@@ -10231,7 +10477,7 @@
         <v>0</v>
       </c>
       <c r="Z75" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA75">
         <v>0</v>
@@ -10246,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="AE75" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF75">
         <v>0</v>
@@ -10261,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="AJ75" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK75">
         <v>0</v>
@@ -10274,6 +10520,9 @@
       </c>
       <c r="AN75">
         <v>0</v>
+      </c>
+      <c r="AO75">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -10281,10 +10530,10 @@
         <v>26020072</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -10335,10 +10584,10 @@
         <v>0</v>
       </c>
       <c r="T76" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U76" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V76">
         <v>0</v>
@@ -10353,7 +10602,7 @@
         <v>0</v>
       </c>
       <c r="Z76" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA76">
         <v>0</v>
@@ -10368,7 +10617,7 @@
         <v>0</v>
       </c>
       <c r="AE76" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF76">
         <v>0</v>
@@ -10383,7 +10632,7 @@
         <v>2000</v>
       </c>
       <c r="AJ76" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK76">
         <v>0</v>
@@ -10395,6 +10644,9 @@
         <v>0</v>
       </c>
       <c r="AN76">
+        <v>0</v>
+      </c>
+      <c r="AO76">
         <v>0</v>
       </c>
     </row>
@@ -10403,10 +10655,10 @@
         <v>26020073</v>
       </c>
       <c r="B77" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D77">
         <v>3</v>
@@ -10457,10 +10709,10 @@
         <v>0</v>
       </c>
       <c r="T77" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U77" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V77">
         <v>0</v>
@@ -10475,7 +10727,7 @@
         <v>0</v>
       </c>
       <c r="Z77" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA77">
         <v>0</v>
@@ -10490,7 +10742,7 @@
         <v>0</v>
       </c>
       <c r="AE77" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF77">
         <v>0</v>
@@ -10505,7 +10757,7 @@
         <v>0</v>
       </c>
       <c r="AJ77" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK77">
         <v>0</v>
@@ -10518,6 +10770,9 @@
       </c>
       <c r="AN77">
         <v>0</v>
+      </c>
+      <c r="AO77">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -10525,10 +10780,10 @@
         <v>26020074</v>
       </c>
       <c r="B78" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C78" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -10579,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="T78" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="U78" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V78">
         <v>0</v>
@@ -10597,7 +10852,7 @@
         <v>0</v>
       </c>
       <c r="Z78" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA78">
         <v>0</v>
@@ -10612,7 +10867,7 @@
         <v>0</v>
       </c>
       <c r="AE78" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF78">
         <v>0</v>
@@ -10627,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="AJ78" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AK78">
         <v>1</v>
@@ -10639,6 +10894,9 @@
         <v>0</v>
       </c>
       <c r="AN78">
+        <v>0</v>
+      </c>
+      <c r="AO78">
         <v>0</v>
       </c>
     </row>
@@ -10647,10 +10905,10 @@
         <v>26020075</v>
       </c>
       <c r="B79" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C79" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D79">
         <v>3</v>
@@ -10701,10 +10959,10 @@
         <v>0</v>
       </c>
       <c r="T79" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U79" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V79">
         <v>0</v>
@@ -10719,7 +10977,7 @@
         <v>0</v>
       </c>
       <c r="Z79" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA79">
         <v>0</v>
@@ -10734,7 +10992,7 @@
         <v>0</v>
       </c>
       <c r="AE79" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF79">
         <v>0</v>
@@ -10749,7 +11007,7 @@
         <v>1500</v>
       </c>
       <c r="AJ79" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK79">
         <v>0</v>
@@ -10762,6 +11020,9 @@
       </c>
       <c r="AN79">
         <v>0</v>
+      </c>
+      <c r="AO79">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -10769,10 +11030,10 @@
         <v>26020076</v>
       </c>
       <c r="B80" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C80" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D80">
         <v>3</v>
@@ -10823,10 +11084,10 @@
         <v>0</v>
       </c>
       <c r="T80" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U80" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V80">
         <v>0</v>
@@ -10841,7 +11102,7 @@
         <v>0</v>
       </c>
       <c r="Z80" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA80">
         <v>0</v>
@@ -10856,7 +11117,7 @@
         <v>0</v>
       </c>
       <c r="AE80" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF80">
         <v>0</v>
@@ -10871,7 +11132,7 @@
         <v>2300</v>
       </c>
       <c r="AJ80" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK80">
         <v>0</v>
@@ -10884,6 +11145,9 @@
       </c>
       <c r="AN80">
         <v>0</v>
+      </c>
+      <c r="AO80">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -10891,10 +11155,10 @@
         <v>26020077</v>
       </c>
       <c r="B81" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C81" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -10945,10 +11209,10 @@
         <v>0</v>
       </c>
       <c r="T81" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U81" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V81">
         <v>0</v>
@@ -10963,7 +11227,7 @@
         <v>0</v>
       </c>
       <c r="Z81" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA81">
         <v>0</v>
@@ -10978,7 +11242,7 @@
         <v>0</v>
       </c>
       <c r="AE81" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF81">
         <v>0</v>
@@ -10993,7 +11257,7 @@
         <v>1800</v>
       </c>
       <c r="AJ81" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK81">
         <v>0</v>
@@ -11005,6 +11269,9 @@
         <v>0</v>
       </c>
       <c r="AN81">
+        <v>0</v>
+      </c>
+      <c r="AO81">
         <v>0</v>
       </c>
     </row>
@@ -11013,10 +11280,10 @@
         <v>26020078</v>
       </c>
       <c r="B82" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C82" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -11067,10 +11334,10 @@
         <v>0</v>
       </c>
       <c r="T82" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U82" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V82">
         <v>0</v>
@@ -11085,7 +11352,7 @@
         <v>0</v>
       </c>
       <c r="Z82" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA82">
         <v>0</v>
@@ -11100,7 +11367,7 @@
         <v>0</v>
       </c>
       <c r="AE82" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF82">
         <v>0</v>
@@ -11115,7 +11382,7 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK82">
         <v>0</v>
@@ -11128,6 +11395,9 @@
       </c>
       <c r="AN82">
         <v>0</v>
+      </c>
+      <c r="AO82">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -11135,10 +11405,10 @@
         <v>26020079</v>
       </c>
       <c r="B83" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C83" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D83">
         <v>3</v>
@@ -11189,10 +11459,10 @@
         <v>0</v>
       </c>
       <c r="T83" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U83" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V83">
         <v>0</v>
@@ -11207,7 +11477,7 @@
         <v>0</v>
       </c>
       <c r="Z83" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA83">
         <v>0</v>
@@ -11222,7 +11492,7 @@
         <v>0</v>
       </c>
       <c r="AE83" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF83">
         <v>0</v>
@@ -11237,7 +11507,7 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK83">
         <v>0</v>
@@ -11250,6 +11520,9 @@
       </c>
       <c r="AN83">
         <v>0</v>
+      </c>
+      <c r="AO83">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -11257,10 +11530,10 @@
         <v>26020080</v>
       </c>
       <c r="B84" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C84" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -11311,10 +11584,10 @@
         <v>0</v>
       </c>
       <c r="T84" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U84" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V84">
         <v>0</v>
@@ -11329,7 +11602,7 @@
         <v>0</v>
       </c>
       <c r="Z84" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA84">
         <v>0</v>
@@ -11344,7 +11617,7 @@
         <v>0</v>
       </c>
       <c r="AE84" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF84">
         <v>0</v>
@@ -11359,7 +11632,7 @@
         <v>1000</v>
       </c>
       <c r="AJ84" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK84">
         <v>0</v>
@@ -11371,6 +11644,9 @@
         <v>0</v>
       </c>
       <c r="AN84">
+        <v>0</v>
+      </c>
+      <c r="AO84">
         <v>0</v>
       </c>
     </row>
@@ -11379,10 +11655,10 @@
         <v>26020081</v>
       </c>
       <c r="B85" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C85" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -11433,10 +11709,10 @@
         <v>0</v>
       </c>
       <c r="T85" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U85" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -11451,7 +11727,7 @@
         <v>0</v>
       </c>
       <c r="Z85" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA85">
         <v>0</v>
@@ -11466,7 +11742,7 @@
         <v>0</v>
       </c>
       <c r="AE85" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF85">
         <v>0</v>
@@ -11481,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="AJ85" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK85">
         <v>0</v>
@@ -11494,6 +11770,9 @@
       </c>
       <c r="AN85">
         <v>0</v>
+      </c>
+      <c r="AO85">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -11501,10 +11780,10 @@
         <v>26020082</v>
       </c>
       <c r="B86" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C86" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -11555,10 +11834,10 @@
         <v>0</v>
       </c>
       <c r="T86" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="U86" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V86">
         <v>0</v>
@@ -11573,7 +11852,7 @@
         <v>30000</v>
       </c>
       <c r="Z86" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA86">
         <v>0</v>
@@ -11588,7 +11867,7 @@
         <v>0</v>
       </c>
       <c r="AE86" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF86">
         <v>0</v>
@@ -11603,7 +11882,7 @@
         <v>0</v>
       </c>
       <c r="AJ86" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK86">
         <v>0</v>
@@ -11615,6 +11894,9 @@
         <v>0</v>
       </c>
       <c r="AN86">
+        <v>0</v>
+      </c>
+      <c r="AO86">
         <v>0</v>
       </c>
     </row>
@@ -11623,10 +11905,10 @@
         <v>26020083</v>
       </c>
       <c r="B87" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C87" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D87">
         <v>3</v>
@@ -11677,10 +11959,10 @@
         <v>0</v>
       </c>
       <c r="T87" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U87" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V87">
         <v>0</v>
@@ -11695,7 +11977,7 @@
         <v>0</v>
       </c>
       <c r="Z87" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA87">
         <v>0</v>
@@ -11710,7 +11992,7 @@
         <v>0</v>
       </c>
       <c r="AE87" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF87">
         <v>0</v>
@@ -11725,7 +12007,7 @@
         <v>0</v>
       </c>
       <c r="AJ87" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK87">
         <v>0</v>
@@ -11738,6 +12020,9 @@
       </c>
       <c r="AN87">
         <v>0</v>
+      </c>
+      <c r="AO87">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -11745,10 +12030,10 @@
         <v>26020084</v>
       </c>
       <c r="B88" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C88" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D88">
         <v>3</v>
@@ -11799,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="T88" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U88" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V88">
         <v>0</v>
@@ -11817,7 +12102,7 @@
         <v>0</v>
       </c>
       <c r="Z88" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA88">
         <v>0</v>
@@ -11832,7 +12117,7 @@
         <v>0</v>
       </c>
       <c r="AE88" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF88">
         <v>0</v>
@@ -11847,7 +12132,7 @@
         <v>2000</v>
       </c>
       <c r="AJ88" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK88">
         <v>0</v>
@@ -11859,6 +12144,9 @@
         <v>0</v>
       </c>
       <c r="AN88">
+        <v>0</v>
+      </c>
+      <c r="AO88">
         <v>0</v>
       </c>
     </row>
@@ -11867,10 +12155,10 @@
         <v>26020085</v>
       </c>
       <c r="B89" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C89" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D89">
         <v>3</v>
@@ -11921,10 +12209,10 @@
         <v>0</v>
       </c>
       <c r="T89" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U89" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V89">
         <v>0</v>
@@ -11939,7 +12227,7 @@
         <v>0</v>
       </c>
       <c r="Z89" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA89">
         <v>0</v>
@@ -11954,7 +12242,7 @@
         <v>0</v>
       </c>
       <c r="AE89" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF89">
         <v>0</v>
@@ -11969,7 +12257,7 @@
         <v>1500</v>
       </c>
       <c r="AJ89" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK89">
         <v>0</v>
@@ -11981,6 +12269,9 @@
         <v>0</v>
       </c>
       <c r="AN89">
+        <v>0</v>
+      </c>
+      <c r="AO89">
         <v>0</v>
       </c>
     </row>
@@ -11989,10 +12280,10 @@
         <v>26020086</v>
       </c>
       <c r="B90" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C90" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -12043,10 +12334,10 @@
         <v>0</v>
       </c>
       <c r="T90" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U90" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V90">
         <v>0</v>
@@ -12061,7 +12352,7 @@
         <v>0</v>
       </c>
       <c r="Z90" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA90">
         <v>0</v>
@@ -12076,7 +12367,7 @@
         <v>0</v>
       </c>
       <c r="AE90" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF90">
         <v>0</v>
@@ -12091,7 +12382,7 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK90">
         <v>0</v>
@@ -12103,6 +12394,9 @@
         <v>0</v>
       </c>
       <c r="AN90">
+        <v>0</v>
+      </c>
+      <c r="AO90">
         <v>0</v>
       </c>
     </row>
@@ -12111,10 +12405,10 @@
         <v>26020087</v>
       </c>
       <c r="B91" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C91" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D91">
         <v>3</v>
@@ -12165,10 +12459,10 @@
         <v>0</v>
       </c>
       <c r="T91" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U91" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V91">
         <v>0</v>
@@ -12183,7 +12477,7 @@
         <v>0</v>
       </c>
       <c r="Z91" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA91">
         <v>0</v>
@@ -12198,7 +12492,7 @@
         <v>0</v>
       </c>
       <c r="AE91" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF91">
         <v>0</v>
@@ -12213,7 +12507,7 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK91">
         <v>0</v>
@@ -12226,6 +12520,9 @@
       </c>
       <c r="AN91">
         <v>0</v>
+      </c>
+      <c r="AO91">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -12233,10 +12530,10 @@
         <v>26020088</v>
       </c>
       <c r="B92" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C92" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D92">
         <v>3</v>
@@ -12287,10 +12584,10 @@
         <v>0</v>
       </c>
       <c r="T92" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U92" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V92">
         <v>0</v>
@@ -12305,7 +12602,7 @@
         <v>0</v>
       </c>
       <c r="Z92" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA92">
         <v>0</v>
@@ -12320,7 +12617,7 @@
         <v>0</v>
       </c>
       <c r="AE92" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF92">
         <v>0</v>
@@ -12335,7 +12632,7 @@
         <v>0</v>
       </c>
       <c r="AJ92" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK92">
         <v>0</v>
@@ -12348,6 +12645,9 @@
       </c>
       <c r="AN92">
         <v>0</v>
+      </c>
+      <c r="AO92">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -12355,10 +12655,10 @@
         <v>26020089</v>
       </c>
       <c r="B93" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C93" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D93">
         <v>3</v>
@@ -12409,10 +12709,10 @@
         <v>0</v>
       </c>
       <c r="T93" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U93" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V93">
         <v>0</v>
@@ -12427,7 +12727,7 @@
         <v>0</v>
       </c>
       <c r="Z93" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA93">
         <v>0</v>
@@ -12442,7 +12742,7 @@
         <v>0</v>
       </c>
       <c r="AE93" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF93">
         <v>0</v>
@@ -12457,7 +12757,7 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK93">
         <v>0</v>
@@ -12470,6 +12770,9 @@
       </c>
       <c r="AN93">
         <v>0</v>
+      </c>
+      <c r="AO93">
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -12477,10 +12780,10 @@
         <v>26020090</v>
       </c>
       <c r="B94" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C94" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -12531,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="T94" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="U94" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V94">
         <v>0</v>
@@ -12549,7 +12852,7 @@
         <v>0</v>
       </c>
       <c r="Z94" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AA94">
         <v>0</v>
@@ -12564,7 +12867,7 @@
         <v>0</v>
       </c>
       <c r="AE94" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AF94">
         <v>0</v>
@@ -12579,7 +12882,7 @@
         <v>0</v>
       </c>
       <c r="AJ94" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK94">
         <v>0</v>
@@ -12592,6 +12895,9 @@
       </c>
       <c r="AN94">
         <v>0</v>
+      </c>
+      <c r="AO94">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
